--- a/questionnaires/RM_Analyst_Questionnaire.xlsx
+++ b/questionnaires/RM_Analyst_Questionnaire.xlsx
@@ -13,12 +13,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test times" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extra tests" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Other materials" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase list" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Volumes'!$A$4:$M$184</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Test times'!$A$8:$AD$282</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Extra tests'!$A$4:$Z$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Other materials'!$A$4:$G$384</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Purchase list'!$A$4:$H$403</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -613,30 +615,30 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sheet: Purchase list</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Names from the purchasing list (rawmaterials.md) - confirm the study name, or say if still tested.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Colour code</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Yellow = you type. Grey = pre-filled from company records - correct it if it is wrong.</t>
-        </is>
-      </c>
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Data basis</t>
+          <t>Colour code</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>180 materials and 274 material x test rows from QC_Capacity_Study.xlsx (RM_Lots, Test_Times).</t>
+          <t>Yellow = you type. Grey = pre-filled from company records - correct it if it is wrong.</t>
         </is>
       </c>
     </row>
@@ -648,7 +650,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Leadtime.xlsx: 69 exact + 84 alias name matches; 122 materials have a recorded time to confirm.</t>
+          <t>180 materials and 274 material x test rows from QC_Capacity_Study.xlsx (RM_Lots, Test_Times).</t>
         </is>
       </c>
     </row>
@@ -660,37 +662,61 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t>Leadtime.xlsx: 69 exact + 84 alias name matches; 122 materials have a recorded time to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Data basis</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>380 materials appear in Leadtime.xlsx but not in the study list - see 'Other materials'.</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Respondent</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
+          <t>Data basis</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>rawmaterials.md: 399 distinct names; 208 Not in study, 87 In study, 59 Suggested - confirm, 19 In study (Leadtime alias), 18 In study (DB name mapping), 8 In Leadtime.xlsx only - see 'Purchase list'.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>Respondent</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>Reviewed by (unit head)</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -37251,4 +37277,8802 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H403"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Raw-material names from the purchasing list (rawmaterials.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Grey = matched automatically. Confirm 'Suggested' rows; for 'Not in study' rows say if QC still tests it and give lots/yr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Name (as in rawmaterials.md)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Times listed</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Match to study</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Study material</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Correct study name (if wrong / missing)</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Still tested by QC? (Y/N)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Lots / yr</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Acetaminophen DC</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Acetaminophen</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Acetaminophen DC 96%</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Acetaminophen</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Azelastine Hydrochloride USP</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Azelastine Hydrochloride</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>B-Carotene</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Beta-Carotene</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>B-Nicotinamide Mononucleotide(NMN)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Nicotinamide Mononucleotide (NMN) Granule</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Biotin-B7</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Biotin (Vitamin B7)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>BRILLIANT BLUE (POWDER)-No. 1</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Brilliant Blue</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Calcium carbonate extra heavy</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Carbonate Heavy</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Carbonate Extre Heavy</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Carbonate Heavy</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Caramel Color</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Caramel Colour</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Cooper Gluconate</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Copper Gluconate</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Croscarmellose Sodium-USP</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Croscarmellose Sodium</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>D-Calcium Pantothenate</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Pantothenate (Vitamin B5)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Dapagliflozin Propandiol Monohydrate</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Dapagliflozin Propanediol Monohydrate</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Devil's Claw Extract</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Devil's Claw Dry Extract 6:1</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Dexlansoprazole Pellets 20 % w/w</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Dexlansoprazole Pellets 20%</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Dexlansoprazole Pellets 20.0% w/w</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Dexlansoprazole Pellets 20%</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Ferrous Bisglycinate-20% Iron</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Ferrous Bisglycinate</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Fluticasone Propionate USP</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Fluticasone Propionate</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>FOLIC ACID-B9</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Folic Acid (Vitamin B9)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Ginger Root Extract 5:1</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Ginger Dry Extract 5:1</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Glycerin</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Glycerine</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Glycerine 99.7%</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Glycerine</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Hard Glatin Capsule</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Hard Gelatin Capsule</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>HPMC K100</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>HPMC K100M (100,000 cps CR)</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>L-Cholin Bitartrate</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Choline Bitartrate</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>L-choline Bitartarate</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Choline Bitartrate</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>L-Choline Bitartrate</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Choline Bitartrate</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Lactose Monohydrate 80 Mesh</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Lactose Monohydrate</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Levocarnitine</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>L-Carnitine (Base)</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Magnesiun Oxide,Heavy</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Magnesium Oxide Heavy</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Menthol</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>L-Menthol</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Metformin Hydrochloride USP</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Metformin Hydrochloride</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Methyl Sulfonyl Methane (MSM)</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Methyl Sulphonyl Methane (MSM)</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Methyl Sulfonyl Methane-MSM</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>Methyl Sulphonyl Methane (MSM)</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline Cellose 101(Avicel 101)</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline Cellulose PH 101</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline Cellulse 101</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline Cellulose PH 101</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline celluose RC591</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline Cellulose RC591</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Nicothinamide (Vitamin B3)</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>Nicotinamide (Vitamin B3)</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>NICOTINAMIDE-B3</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Nicotinamide (Vitamin B3)</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Orang Flavour</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Orange Flavour</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Orange Flavor</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Orange Flavour</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Panax Ginseng Extract</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>Panax Ginseng (Asian Ginseng) Dry Extract 3:1</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Panax Ginseng Extract-10%</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Panax Ginseng (Asian Ginseng) Dry Extract 3:1</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Peppermint Extract</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Peppermint Dry Extract</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Peppermint Root Extract</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Peppermint Dry Extract</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Permix Dermobella</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>Premix Dermo Bella</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Ribflavin-B2</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Riboflavin (Vitamin B2)</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>Riboflavine (Vitamin B2)</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Riboflavin (Vitamin B2)</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Saiberian Ginseng Extract</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Siberian Ginseng Dry Extract 5:1</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Saw Palmetto Extract</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>Saw Palmetto Dry Extract 4:1</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Siberian Ginseng Extract</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>Siberian Ginseng Dry Extract 5:1</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Banzoate</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Benzoate</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Stawberry Flavour</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Strawberry Flavour</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Strawberry Flavor</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>Strawberry Flavour</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>SUNSET YELLOW FCF</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Sunset Yellow</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>Tocopheryl Acetate 50%(Vitamin E)</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>D-Alpha Tocopheryl Acetate 50% (Vitamin E)</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>Tribulus terrestris Extract</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>Tribulus Terrestris Dry Extract 50:1</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>Trisodium Citrate Dihydrate</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Suggested - confirm</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Citrate Dihydrate</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Aerosil</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>all-rac-a-Tocopheryl Acetate Powder</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>All-rac-a-Tocopheryl Acetate powder(Vit-E)-50%</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>Anhydrous Dibasic Calcium Phosphate</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>Apium</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>Apium Graveolens Extract</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Apixaban Granule 2.5%</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>Apixaban micronized</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>Appel Green</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>Apple Green R3030</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>Artichoke</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>Artichoke Exteract Powder</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Artichoke extract powder</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>Avicel 102</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>B-Nicotinamide Mononucleotide NMN Powder</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>Benzalkonim Chloride</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>Beta Carotene Powder-10%</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>beta-carotene powder</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n"/>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>Betadex Sulfobutly Ether Sodium</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>Black Coninor E-172</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>Blue color number 2</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Silicate</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n"/>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>Caramel Flavour</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n"/>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>Caramel Powder Color</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>Chlorphenamine Maleate</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n"/>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>Chlorpheniramine maleate</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>CHOCOLATI BROWN HT</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n"/>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>Coated Ascorbic Acid</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n"/>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>Coated Ascorbic Acid- 97 (Vitamin C)</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n"/>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>Coenzyme Q10</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>Coenzyme Q10 98%Coenzyme Q10</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>Coleus Forskohlii</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n"/>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>Coleus Forskohlii Extract</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>Coleus froskohlii Extract</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n"/>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>Compritol</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n"/>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>Compritol 888 ATP</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n"/>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="n"/>
+      <c r="H99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>Corn Starch 1500 (Pergelatinized)</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n"/>
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="5" t="n"/>
+      <c r="G100" s="5" t="n"/>
+      <c r="H100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>Cranberry Extract</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n"/>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="n"/>
+      <c r="H101" s="5" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>Damiana Extract</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n"/>
+      <c r="E102" s="5" t="n"/>
+      <c r="F102" s="5" t="n"/>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="5" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>Damiana Extract 10:1</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n"/>
+      <c r="E103" s="5" t="n"/>
+      <c r="F103" s="5" t="n"/>
+      <c r="G103" s="5" t="n"/>
+      <c r="H103" s="5" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>Devil's Claw</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n"/>
+      <c r="E104" s="5" t="n"/>
+      <c r="F104" s="5" t="n"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="5" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>Dextromethorphan Hydrobromide</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n"/>
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="5" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="5" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>Dicalcium Phosphate (Calcium Hydrogen Phosphate )</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n"/>
+      <c r="E106" s="5" t="n"/>
+      <c r="F106" s="5" t="n"/>
+      <c r="G106" s="5" t="n"/>
+      <c r="H106" s="5" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>Echinacea purpurea L</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n"/>
+      <c r="E107" s="5" t="n"/>
+      <c r="F107" s="5" t="n"/>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="5" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>Empty Hard Gelatin Capsule Shell</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n"/>
+      <c r="E108" s="5" t="n"/>
+      <c r="F108" s="5" t="n"/>
+      <c r="G108" s="5" t="n"/>
+      <c r="H108" s="5" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>Epimedium Extract</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n"/>
+      <c r="E109" s="5" t="n"/>
+      <c r="F109" s="5" t="n"/>
+      <c r="G109" s="5" t="n"/>
+      <c r="H109" s="5" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>Eudragit</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n"/>
+      <c r="E110" s="5" t="n"/>
+      <c r="F110" s="5" t="n"/>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="5" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>FD&amp;C Red NO.40</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n"/>
+      <c r="E111" s="5" t="n"/>
+      <c r="F111" s="5" t="n"/>
+      <c r="G111" s="5" t="n"/>
+      <c r="H111" s="5" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>FD&amp;C RED No.40-ALLURA RED( E129)</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n"/>
+      <c r="E112" s="5" t="n"/>
+      <c r="F112" s="5" t="n"/>
+      <c r="G112" s="5" t="n"/>
+      <c r="H112" s="5" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>Fennel Seed Extract</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n"/>
+      <c r="E113" s="5" t="n"/>
+      <c r="F113" s="5" t="n"/>
+      <c r="G113" s="5" t="n"/>
+      <c r="H113" s="5" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>Fish Oil (Omega 3)</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n"/>
+      <c r="E114" s="5" t="n"/>
+      <c r="F114" s="5" t="n"/>
+      <c r="G114" s="5" t="n"/>
+      <c r="H114" s="5" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>Flax Seeds</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n"/>
+      <c r="E115" s="5" t="n"/>
+      <c r="F115" s="5" t="n"/>
+      <c r="G115" s="5" t="n"/>
+      <c r="H115" s="5" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>Flax Seeds Extract</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n"/>
+      <c r="E116" s="5" t="n"/>
+      <c r="F116" s="5" t="n"/>
+      <c r="G116" s="5" t="n"/>
+      <c r="H116" s="5" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>Flax Seeds Extract-Omega 3</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n"/>
+      <c r="E117" s="5" t="n"/>
+      <c r="F117" s="5" t="n"/>
+      <c r="G117" s="5" t="n"/>
+      <c r="H117" s="5" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>Foil Brinux 90</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n"/>
+      <c r="E118" s="5" t="n"/>
+      <c r="F118" s="5" t="n"/>
+      <c r="G118" s="5" t="n"/>
+      <c r="H118" s="5" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>Foil Vitamin C 150mg</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n"/>
+      <c r="E119" s="5" t="n"/>
+      <c r="F119" s="5" t="n"/>
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="5" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>Fumaric Acid</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n"/>
+      <c r="E120" s="5" t="n"/>
+      <c r="F120" s="5" t="n"/>
+      <c r="G120" s="5" t="n"/>
+      <c r="H120" s="5" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>Garcinia Cambogia</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n"/>
+      <c r="E121" s="5" t="n"/>
+      <c r="F121" s="5" t="n"/>
+      <c r="G121" s="5" t="n"/>
+      <c r="H121" s="5" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>Garcinia Cambogia Extract</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n"/>
+      <c r="E122" s="5" t="n"/>
+      <c r="F122" s="5" t="n"/>
+      <c r="G122" s="5" t="n"/>
+      <c r="H122" s="5" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>Garcinia Cimbogia</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n"/>
+      <c r="E123" s="5" t="n"/>
+      <c r="F123" s="5" t="n"/>
+      <c r="G123" s="5" t="n"/>
+      <c r="H123" s="5" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>GB Green C&amp;F</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n"/>
+      <c r="E124" s="5" t="n"/>
+      <c r="F124" s="5" t="n"/>
+      <c r="G124" s="5" t="n"/>
+      <c r="H124" s="5" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>Gentian Root</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n"/>
+      <c r="E125" s="5" t="n"/>
+      <c r="F125" s="5" t="n"/>
+      <c r="G125" s="5" t="n"/>
+      <c r="H125" s="5" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>Gentian Root Extract</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n"/>
+      <c r="E126" s="5" t="n"/>
+      <c r="F126" s="5" t="n"/>
+      <c r="G126" s="5" t="n"/>
+      <c r="H126" s="5" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>Ginger Extract</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n"/>
+      <c r="E127" s="5" t="n"/>
+      <c r="F127" s="5" t="n"/>
+      <c r="G127" s="5" t="n"/>
+      <c r="H127" s="5" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>Ginger Root</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n"/>
+      <c r="E128" s="5" t="n"/>
+      <c r="F128" s="5" t="n"/>
+      <c r="G128" s="5" t="n"/>
+      <c r="H128" s="5" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>Ginger Root Extract</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n"/>
+      <c r="E129" s="5" t="n"/>
+      <c r="F129" s="5" t="n"/>
+      <c r="G129" s="5" t="n"/>
+      <c r="H129" s="5" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>Ginkgo Biloba</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n"/>
+      <c r="E130" s="5" t="n"/>
+      <c r="F130" s="5" t="n"/>
+      <c r="G130" s="5" t="n"/>
+      <c r="H130" s="5" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>Ginkgo Biloba Extract</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n"/>
+      <c r="E131" s="5" t="n"/>
+      <c r="F131" s="5" t="n"/>
+      <c r="G131" s="5" t="n"/>
+      <c r="H131" s="5" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>Ginkgo Biloba L.</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n"/>
+      <c r="E132" s="5" t="n"/>
+      <c r="F132" s="5" t="n"/>
+      <c r="G132" s="5" t="n"/>
+      <c r="H132" s="5" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>Ginseng Extract 10% Ginsenosides</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n"/>
+      <c r="E133" s="5" t="n"/>
+      <c r="F133" s="5" t="n"/>
+      <c r="G133" s="5" t="n"/>
+      <c r="H133" s="5" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>Gymnema Sylvestre</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n"/>
+      <c r="E134" s="5" t="n"/>
+      <c r="F134" s="5" t="n"/>
+      <c r="G134" s="5" t="n"/>
+      <c r="H134" s="5" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>Gymnema Sylvestre Extract</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n"/>
+      <c r="E135" s="5" t="n"/>
+      <c r="F135" s="5" t="n"/>
+      <c r="G135" s="5" t="n"/>
+      <c r="H135" s="5" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>Hard gelatin (Blue-Dark Blue) Size 1</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n"/>
+      <c r="E136" s="5" t="n"/>
+      <c r="F136" s="5" t="n"/>
+      <c r="G136" s="5" t="n"/>
+      <c r="H136" s="5" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>Hard gelatin (Yellow-Yellow) Size 2</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n"/>
+      <c r="E137" s="5" t="n"/>
+      <c r="F137" s="5" t="n"/>
+      <c r="G137" s="5" t="n"/>
+      <c r="H137" s="5" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>Hard Gelatin Capsule Brown Size 1</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n"/>
+      <c r="E138" s="5" t="n"/>
+      <c r="F138" s="5" t="n"/>
+      <c r="G138" s="5" t="n"/>
+      <c r="H138" s="5" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>HPMC</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n"/>
+      <c r="E139" s="5" t="n"/>
+      <c r="F139" s="5" t="n"/>
+      <c r="G139" s="5" t="n"/>
+      <c r="H139" s="5" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>HPMC 15</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n"/>
+      <c r="E140" s="5" t="n"/>
+      <c r="F140" s="5" t="n"/>
+      <c r="G140" s="5" t="n"/>
+      <c r="H140" s="5" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>HPMC 6E</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n"/>
+      <c r="E141" s="5" t="n"/>
+      <c r="F141" s="5" t="n"/>
+      <c r="G141" s="5" t="n"/>
+      <c r="H141" s="5" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>HPMC E6</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n"/>
+      <c r="E142" s="5" t="n"/>
+      <c r="F142" s="5" t="n"/>
+      <c r="G142" s="5" t="n"/>
+      <c r="H142" s="5" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>Hydrochloricacid furming 37%</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n"/>
+      <c r="E143" s="5" t="n"/>
+      <c r="F143" s="5" t="n"/>
+      <c r="G143" s="5" t="n"/>
+      <c r="H143" s="5" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>Hydroxy Propyl Methyl Cellulose-6</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n"/>
+      <c r="E144" s="5" t="n"/>
+      <c r="F144" s="5" t="n"/>
+      <c r="G144" s="5" t="n"/>
+      <c r="H144" s="5" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>Hydroxypropyl Methyl Cellulose E15</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n"/>
+      <c r="E145" s="5" t="n"/>
+      <c r="F145" s="5" t="n"/>
+      <c r="G145" s="5" t="n"/>
+      <c r="H145" s="5" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>Hydroxypropyl Methyl Cellulose E6</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n"/>
+      <c r="E146" s="5" t="n"/>
+      <c r="F146" s="5" t="n"/>
+      <c r="G146" s="5" t="n"/>
+      <c r="H146" s="5" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>Hypromellose-6</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n"/>
+      <c r="E147" s="5" t="n"/>
+      <c r="F147" s="5" t="n"/>
+      <c r="G147" s="5" t="n"/>
+      <c r="H147" s="5" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>Hypromellose-E-15</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n"/>
+      <c r="E148" s="5" t="n"/>
+      <c r="F148" s="5" t="n"/>
+      <c r="G148" s="5" t="n"/>
+      <c r="H148" s="5" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>Hypromellose-K4m</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n"/>
+      <c r="E149" s="5" t="n"/>
+      <c r="F149" s="5" t="n"/>
+      <c r="G149" s="5" t="n"/>
+      <c r="H149" s="5" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>Iron Bis Glycinate</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n"/>
+      <c r="E150" s="5" t="n"/>
+      <c r="F150" s="5" t="n"/>
+      <c r="G150" s="5" t="n"/>
+      <c r="H150" s="5" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>Juniper Communis</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n"/>
+      <c r="E151" s="5" t="n"/>
+      <c r="F151" s="5" t="n"/>
+      <c r="G151" s="5" t="n"/>
+      <c r="H151" s="5" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>Juniper Communis Extract</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n"/>
+      <c r="E152" s="5" t="n"/>
+      <c r="F152" s="5" t="n"/>
+      <c r="G152" s="5" t="n"/>
+      <c r="H152" s="5" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>Juniper Extract</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n"/>
+      <c r="E153" s="5" t="n"/>
+      <c r="F153" s="5" t="n"/>
+      <c r="G153" s="5" t="n"/>
+      <c r="H153" s="5" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>Kollidon VA64</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n"/>
+      <c r="E154" s="5" t="n"/>
+      <c r="F154" s="5" t="n"/>
+      <c r="G154" s="5" t="n"/>
+      <c r="H154" s="5" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>Kovidone VA64</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n"/>
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="5" t="n"/>
+      <c r="G155" s="5" t="n"/>
+      <c r="H155" s="5" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>L Arginine Base</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n"/>
+      <c r="E156" s="5" t="n"/>
+      <c r="F156" s="5" t="n"/>
+      <c r="G156" s="5" t="n"/>
+      <c r="H156" s="5" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>Lactose</t>
+        </is>
+      </c>
+      <c r="B157" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n"/>
+      <c r="E157" s="5" t="n"/>
+      <c r="F157" s="5" t="n"/>
+      <c r="G157" s="5" t="n"/>
+      <c r="H157" s="5" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>Lactose Monohydrate 200 Mesh</t>
+        </is>
+      </c>
+      <c r="B158" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n"/>
+      <c r="E158" s="5" t="n"/>
+      <c r="F158" s="5" t="n"/>
+      <c r="G158" s="5" t="n"/>
+      <c r="H158" s="5" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>Lactose Monohydrate Granulac 80</t>
+        </is>
+      </c>
+      <c r="B159" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n"/>
+      <c r="E159" s="5" t="n"/>
+      <c r="F159" s="5" t="n"/>
+      <c r="G159" s="5" t="n"/>
+      <c r="H159" s="5" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>Licorice Etraacted Powder</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n"/>
+      <c r="E160" s="5" t="n"/>
+      <c r="F160" s="5" t="n"/>
+      <c r="G160" s="5" t="n"/>
+      <c r="H160" s="5" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>Licorice Extraacted Powder</t>
+        </is>
+      </c>
+      <c r="B161" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n"/>
+      <c r="E161" s="5" t="n"/>
+      <c r="F161" s="5" t="n"/>
+      <c r="G161" s="5" t="n"/>
+      <c r="H161" s="5" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>Licorice Extract Powder</t>
+        </is>
+      </c>
+      <c r="B162" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n"/>
+      <c r="E162" s="5" t="n"/>
+      <c r="F162" s="5" t="n"/>
+      <c r="G162" s="5" t="n"/>
+      <c r="H162" s="5" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>Linaclotide IR Pellets 0.09% w/w</t>
+        </is>
+      </c>
+      <c r="B163" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n"/>
+      <c r="E163" s="5" t="n"/>
+      <c r="F163" s="5" t="n"/>
+      <c r="G163" s="5" t="n"/>
+      <c r="H163" s="5" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>Lipofer</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n"/>
+      <c r="E164" s="5" t="n"/>
+      <c r="F164" s="5" t="n"/>
+      <c r="G164" s="5" t="n"/>
+      <c r="H164" s="5" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>Loperamid Hydrochloride BP</t>
+        </is>
+      </c>
+      <c r="B165" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n"/>
+      <c r="E165" s="5" t="n"/>
+      <c r="F165" s="5" t="n"/>
+      <c r="G165" s="5" t="n"/>
+      <c r="H165" s="5" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>Mannitol 200 SD</t>
+        </is>
+      </c>
+      <c r="B166" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n"/>
+      <c r="E166" s="5" t="n"/>
+      <c r="F166" s="5" t="n"/>
+      <c r="G166" s="5" t="n"/>
+      <c r="H166" s="5" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>Mapcol Allura Red</t>
+        </is>
+      </c>
+      <c r="B167" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n"/>
+      <c r="E167" s="5" t="n"/>
+      <c r="F167" s="5" t="n"/>
+      <c r="G167" s="5" t="n"/>
+      <c r="H167" s="5" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="9" t="inlineStr">
+        <is>
+          <t>Marshmallow</t>
+        </is>
+      </c>
+      <c r="B168" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n"/>
+      <c r="E168" s="5" t="n"/>
+      <c r="F168" s="5" t="n"/>
+      <c r="G168" s="5" t="n"/>
+      <c r="H168" s="5" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>Marshmallow Root</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n"/>
+      <c r="E169" s="5" t="n"/>
+      <c r="F169" s="5" t="n"/>
+      <c r="G169" s="5" t="n"/>
+      <c r="H169" s="5" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>Marshmallow Root Extract</t>
+        </is>
+      </c>
+      <c r="B170" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n"/>
+      <c r="E170" s="5" t="n"/>
+      <c r="F170" s="5" t="n"/>
+      <c r="G170" s="5" t="n"/>
+      <c r="H170" s="5" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>Melatonin BP</t>
+        </is>
+      </c>
+      <c r="B171" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n"/>
+      <c r="E171" s="5" t="n"/>
+      <c r="F171" s="5" t="n"/>
+      <c r="G171" s="5" t="n"/>
+      <c r="H171" s="5" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>Menthol Crystal</t>
+        </is>
+      </c>
+      <c r="B172" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n"/>
+      <c r="E172" s="5" t="n"/>
+      <c r="F172" s="5" t="n"/>
+      <c r="G172" s="5" t="n"/>
+      <c r="H172" s="5" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>Menthol Crystals</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n"/>
+      <c r="E173" s="5" t="n"/>
+      <c r="F173" s="5" t="n"/>
+      <c r="G173" s="5" t="n"/>
+      <c r="H173" s="5" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>Methacrylic Acid Ethyl Acrylate Copolymer-L100</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n"/>
+      <c r="E174" s="5" t="n"/>
+      <c r="F174" s="5" t="n"/>
+      <c r="G174" s="5" t="n"/>
+      <c r="H174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline 101</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n"/>
+      <c r="E175" s="5" t="n"/>
+      <c r="F175" s="5" t="n"/>
+      <c r="G175" s="5" t="n"/>
+      <c r="H175" s="5" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>Naproxen Base</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n"/>
+      <c r="E176" s="5" t="n"/>
+      <c r="F176" s="5" t="n"/>
+      <c r="G176" s="5" t="n"/>
+      <c r="H176" s="5" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>Neelicol Caramel</t>
+        </is>
+      </c>
+      <c r="B177" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n"/>
+      <c r="E177" s="5" t="n"/>
+      <c r="F177" s="5" t="n"/>
+      <c r="G177" s="5" t="n"/>
+      <c r="H177" s="5" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>Orforglipron hemicalcium (OGLG)</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n"/>
+      <c r="E178" s="5" t="n"/>
+      <c r="F178" s="5" t="n"/>
+      <c r="G178" s="5" t="n"/>
+      <c r="H178" s="5" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>OXIDE IRON RED</t>
+        </is>
+      </c>
+      <c r="B179" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C179" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n"/>
+      <c r="E179" s="5" t="n"/>
+      <c r="F179" s="5" t="n"/>
+      <c r="G179" s="5" t="n"/>
+      <c r="H179" s="5" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>Ozonimod</t>
+        </is>
+      </c>
+      <c r="B180" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n"/>
+      <c r="E180" s="5" t="n"/>
+      <c r="F180" s="5" t="n"/>
+      <c r="G180" s="5" t="n"/>
+      <c r="H180" s="5" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>Panax Ginseng Extract 3% Ginsenosides</t>
+        </is>
+      </c>
+      <c r="B181" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n"/>
+      <c r="E181" s="5" t="n"/>
+      <c r="F181" s="5" t="n"/>
+      <c r="G181" s="5" t="n"/>
+      <c r="H181" s="5" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>Passion Flower Extract</t>
+        </is>
+      </c>
+      <c r="B182" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n"/>
+      <c r="E182" s="5" t="n"/>
+      <c r="F182" s="5" t="n"/>
+      <c r="G182" s="5" t="n"/>
+      <c r="H182" s="5" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>PEG 400</t>
+        </is>
+      </c>
+      <c r="B183" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n"/>
+      <c r="E183" s="5" t="n"/>
+      <c r="F183" s="5" t="n"/>
+      <c r="G183" s="5" t="n"/>
+      <c r="H183" s="5" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="9" t="inlineStr">
+        <is>
+          <t>Peppermint</t>
+        </is>
+      </c>
+      <c r="B184" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n"/>
+      <c r="E184" s="5" t="n"/>
+      <c r="F184" s="5" t="n"/>
+      <c r="G184" s="5" t="n"/>
+      <c r="H184" s="5" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>Permix Burning Fat</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n"/>
+      <c r="E185" s="5" t="n"/>
+      <c r="F185" s="5" t="n"/>
+      <c r="G185" s="5" t="n"/>
+      <c r="H185" s="5" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="inlineStr">
+        <is>
+          <t>Permix Celer-X Forte</t>
+        </is>
+      </c>
+      <c r="B186" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n"/>
+      <c r="E186" s="5" t="n"/>
+      <c r="F186" s="5" t="n"/>
+      <c r="G186" s="5" t="n"/>
+      <c r="H186" s="5" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>Permix Digestive Aid</t>
+        </is>
+      </c>
+      <c r="B187" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n"/>
+      <c r="E187" s="5" t="n"/>
+      <c r="F187" s="5" t="n"/>
+      <c r="G187" s="5" t="n"/>
+      <c r="H187" s="5" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="9" t="inlineStr">
+        <is>
+          <t>Permix Energe-X</t>
+        </is>
+      </c>
+      <c r="B188" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C188" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n"/>
+      <c r="E188" s="5" t="n"/>
+      <c r="F188" s="5" t="n"/>
+      <c r="G188" s="5" t="n"/>
+      <c r="H188" s="5" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t>Permix FerOral</t>
+        </is>
+      </c>
+      <c r="B189" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n"/>
+      <c r="E189" s="5" t="n"/>
+      <c r="F189" s="5" t="n"/>
+      <c r="G189" s="5" t="n"/>
+      <c r="H189" s="5" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="9" t="inlineStr">
+        <is>
+          <t>Permix Ginc Active</t>
+        </is>
+      </c>
+      <c r="B190" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n"/>
+      <c r="E190" s="5" t="n"/>
+      <c r="F190" s="5" t="n"/>
+      <c r="G190" s="5" t="n"/>
+      <c r="H190" s="5" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="9" t="inlineStr">
+        <is>
+          <t>Permix Healthy Liver</t>
+        </is>
+      </c>
+      <c r="B191" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n"/>
+      <c r="E191" s="5" t="n"/>
+      <c r="F191" s="5" t="n"/>
+      <c r="G191" s="5" t="n"/>
+      <c r="H191" s="5" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="9" t="inlineStr">
+        <is>
+          <t>Permix Kamasotra</t>
+        </is>
+      </c>
+      <c r="B192" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n"/>
+      <c r="E192" s="5" t="n"/>
+      <c r="F192" s="5" t="n"/>
+      <c r="G192" s="5" t="n"/>
+      <c r="H192" s="5" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>Permix Optiwoman</t>
+        </is>
+      </c>
+      <c r="B193" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n"/>
+      <c r="E193" s="5" t="n"/>
+      <c r="F193" s="5" t="n"/>
+      <c r="G193" s="5" t="n"/>
+      <c r="H193" s="5" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>Permix Painlys</t>
+        </is>
+      </c>
+      <c r="B194" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="n"/>
+      <c r="E194" s="5" t="n"/>
+      <c r="F194" s="5" t="n"/>
+      <c r="G194" s="5" t="n"/>
+      <c r="H194" s="5" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="9" t="inlineStr">
+        <is>
+          <t>Permix Pregnalife</t>
+        </is>
+      </c>
+      <c r="B195" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="n"/>
+      <c r="E195" s="5" t="n"/>
+      <c r="F195" s="5" t="n"/>
+      <c r="G195" s="5" t="n"/>
+      <c r="H195" s="5" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>Permix Prostica</t>
+        </is>
+      </c>
+      <c r="B196" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="n"/>
+      <c r="E196" s="5" t="n"/>
+      <c r="F196" s="5" t="n"/>
+      <c r="G196" s="5" t="n"/>
+      <c r="H196" s="5" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>Permix Uromax</t>
+        </is>
+      </c>
+      <c r="B197" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C197" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="n"/>
+      <c r="E197" s="5" t="n"/>
+      <c r="F197" s="5" t="n"/>
+      <c r="G197" s="5" t="n"/>
+      <c r="H197" s="5" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="inlineStr">
+        <is>
+          <t>Permix Vitacal Forte</t>
+        </is>
+      </c>
+      <c r="B198" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="n"/>
+      <c r="E198" s="5" t="n"/>
+      <c r="F198" s="5" t="n"/>
+      <c r="G198" s="5" t="n"/>
+      <c r="H198" s="5" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>Permix Vitacl Forte</t>
+        </is>
+      </c>
+      <c r="B199" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="n"/>
+      <c r="E199" s="5" t="n"/>
+      <c r="F199" s="5" t="n"/>
+      <c r="G199" s="5" t="n"/>
+      <c r="H199" s="5" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="9" t="inlineStr">
+        <is>
+          <t>Permix X-Ade</t>
+        </is>
+      </c>
+      <c r="B200" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C200" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="n"/>
+      <c r="E200" s="5" t="n"/>
+      <c r="F200" s="5" t="n"/>
+      <c r="G200" s="5" t="n"/>
+      <c r="H200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="9" t="inlineStr">
+        <is>
+          <t>Phenylephrine Hydrochloride</t>
+        </is>
+      </c>
+      <c r="B201" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C201" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D201" s="9" t="n"/>
+      <c r="E201" s="5" t="n"/>
+      <c r="F201" s="5" t="n"/>
+      <c r="G201" s="5" t="n"/>
+      <c r="H201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="9" t="inlineStr">
+        <is>
+          <t>Potassium Hydroxide Solutin</t>
+        </is>
+      </c>
+      <c r="B202" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C202" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D202" s="9" t="n"/>
+      <c r="E202" s="5" t="n"/>
+      <c r="F202" s="5" t="n"/>
+      <c r="G202" s="5" t="n"/>
+      <c r="H202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="9" t="inlineStr">
+        <is>
+          <t>Potassium Phosphate Monobasic</t>
+        </is>
+      </c>
+      <c r="B203" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D203" s="9" t="n"/>
+      <c r="E203" s="5" t="n"/>
+      <c r="F203" s="5" t="n"/>
+      <c r="G203" s="5" t="n"/>
+      <c r="H203" s="5" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="9" t="inlineStr">
+        <is>
+          <t>Potassium Sorbate Food Grade</t>
+        </is>
+      </c>
+      <c r="B204" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D204" s="9" t="n"/>
+      <c r="E204" s="5" t="n"/>
+      <c r="F204" s="5" t="n"/>
+      <c r="G204" s="5" t="n"/>
+      <c r="H204" s="5" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="9" t="inlineStr">
+        <is>
+          <t>Povidone</t>
+        </is>
+      </c>
+      <c r="B205" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C205" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="n"/>
+      <c r="E205" s="5" t="n"/>
+      <c r="F205" s="5" t="n"/>
+      <c r="G205" s="5" t="n"/>
+      <c r="H205" s="5" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="9" t="inlineStr">
+        <is>
+          <t>Povidone K90</t>
+        </is>
+      </c>
+      <c r="B206" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D206" s="9" t="n"/>
+      <c r="E206" s="5" t="n"/>
+      <c r="F206" s="5" t="n"/>
+      <c r="G206" s="5" t="n"/>
+      <c r="H206" s="5" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="9" t="inlineStr">
+        <is>
+          <t>Premix Powder of Burning Fat</t>
+        </is>
+      </c>
+      <c r="B207" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D207" s="9" t="n"/>
+      <c r="E207" s="5" t="n"/>
+      <c r="F207" s="5" t="n"/>
+      <c r="G207" s="5" t="n"/>
+      <c r="H207" s="5" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="9" t="inlineStr">
+        <is>
+          <t>Premix Powder of Celerex</t>
+        </is>
+      </c>
+      <c r="B208" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D208" s="9" t="n"/>
+      <c r="E208" s="5" t="n"/>
+      <c r="F208" s="5" t="n"/>
+      <c r="G208" s="5" t="n"/>
+      <c r="H208" s="5" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="9" t="inlineStr">
+        <is>
+          <t>Premix Powder of Dermobella</t>
+        </is>
+      </c>
+      <c r="B209" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D209" s="9" t="n"/>
+      <c r="E209" s="5" t="n"/>
+      <c r="F209" s="5" t="n"/>
+      <c r="G209" s="5" t="n"/>
+      <c r="H209" s="5" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>Premix Powder of Digestive Aid</t>
+        </is>
+      </c>
+      <c r="B210" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D210" s="9" t="n"/>
+      <c r="E210" s="5" t="n"/>
+      <c r="F210" s="5" t="n"/>
+      <c r="G210" s="5" t="n"/>
+      <c r="H210" s="5" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="9" t="inlineStr">
+        <is>
+          <t>Premix powder of Energex</t>
+        </is>
+      </c>
+      <c r="B211" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D211" s="9" t="n"/>
+      <c r="E211" s="5" t="n"/>
+      <c r="F211" s="5" t="n"/>
+      <c r="G211" s="5" t="n"/>
+      <c r="H211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="9" t="inlineStr">
+        <is>
+          <t>Premix powder of healthy Liver</t>
+        </is>
+      </c>
+      <c r="B212" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D212" s="9" t="n"/>
+      <c r="E212" s="5" t="n"/>
+      <c r="F212" s="5" t="n"/>
+      <c r="G212" s="5" t="n"/>
+      <c r="H212" s="5" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="9" t="inlineStr">
+        <is>
+          <t>Premix Powder of Optiwoman</t>
+        </is>
+      </c>
+      <c r="B213" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D213" s="9" t="n"/>
+      <c r="E213" s="5" t="n"/>
+      <c r="F213" s="5" t="n"/>
+      <c r="G213" s="5" t="n"/>
+      <c r="H213" s="5" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="9" t="inlineStr">
+        <is>
+          <t>Premix Powder of Painlys</t>
+        </is>
+      </c>
+      <c r="B214" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D214" s="9" t="n"/>
+      <c r="E214" s="5" t="n"/>
+      <c r="F214" s="5" t="n"/>
+      <c r="G214" s="5" t="n"/>
+      <c r="H214" s="5" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="9" t="inlineStr">
+        <is>
+          <t>Premix Powder of Pregna Life</t>
+        </is>
+      </c>
+      <c r="B215" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D215" s="9" t="n"/>
+      <c r="E215" s="5" t="n"/>
+      <c r="F215" s="5" t="n"/>
+      <c r="G215" s="5" t="n"/>
+      <c r="H215" s="5" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="9" t="inlineStr">
+        <is>
+          <t>Premix Powder of Prostica</t>
+        </is>
+      </c>
+      <c r="B216" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D216" s="9" t="n"/>
+      <c r="E216" s="5" t="n"/>
+      <c r="F216" s="5" t="n"/>
+      <c r="G216" s="5" t="n"/>
+      <c r="H216" s="5" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="9" t="inlineStr">
+        <is>
+          <t>Premix Powder of Uromax</t>
+        </is>
+      </c>
+      <c r="B217" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="n"/>
+      <c r="E217" s="5" t="n"/>
+      <c r="F217" s="5" t="n"/>
+      <c r="G217" s="5" t="n"/>
+      <c r="H217" s="5" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="9" t="inlineStr">
+        <is>
+          <t>Premix Powder of X-Ade</t>
+        </is>
+      </c>
+      <c r="B218" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D218" s="9" t="n"/>
+      <c r="E218" s="5" t="n"/>
+      <c r="F218" s="5" t="n"/>
+      <c r="G218" s="5" t="n"/>
+      <c r="H218" s="5" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="9" t="inlineStr">
+        <is>
+          <t>Premix powder Optiwoman</t>
+        </is>
+      </c>
+      <c r="B219" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D219" s="9" t="n"/>
+      <c r="E219" s="5" t="n"/>
+      <c r="F219" s="5" t="n"/>
+      <c r="G219" s="5" t="n"/>
+      <c r="H219" s="5" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="9" t="inlineStr">
+        <is>
+          <t>Propan-2-ol</t>
+        </is>
+      </c>
+      <c r="B220" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C220" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D220" s="9" t="n"/>
+      <c r="E220" s="5" t="n"/>
+      <c r="F220" s="5" t="n"/>
+      <c r="G220" s="5" t="n"/>
+      <c r="H220" s="5" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="9" t="inlineStr">
+        <is>
+          <t>Purple Coneflower dry extra(Echinacea Purpurea)</t>
+        </is>
+      </c>
+      <c r="B221" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D221" s="9" t="n"/>
+      <c r="E221" s="5" t="n"/>
+      <c r="F221" s="5" t="n"/>
+      <c r="G221" s="5" t="n"/>
+      <c r="H221" s="5" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="9" t="inlineStr">
+        <is>
+          <t>PVP (K30)</t>
+        </is>
+      </c>
+      <c r="B222" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C222" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D222" s="9" t="n"/>
+      <c r="E222" s="5" t="n"/>
+      <c r="F222" s="5" t="n"/>
+      <c r="G222" s="5" t="n"/>
+      <c r="H222" s="5" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t>Resmetirom -DC Granules 20 % w/w</t>
+        </is>
+      </c>
+      <c r="B223" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D223" s="9" t="n"/>
+      <c r="E223" s="5" t="n"/>
+      <c r="F223" s="5" t="n"/>
+      <c r="G223" s="5" t="n"/>
+      <c r="H223" s="5" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="9" t="inlineStr">
+        <is>
+          <t>Royal Jelly Powder</t>
+        </is>
+      </c>
+      <c r="B224" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D224" s="9" t="n"/>
+      <c r="E224" s="5" t="n"/>
+      <c r="F224" s="5" t="n"/>
+      <c r="G224" s="5" t="n"/>
+      <c r="H224" s="5" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="9" t="inlineStr">
+        <is>
+          <t>SACHELAC®80</t>
+        </is>
+      </c>
+      <c r="B225" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D225" s="9" t="n"/>
+      <c r="E225" s="5" t="n"/>
+      <c r="F225" s="5" t="n"/>
+      <c r="G225" s="5" t="n"/>
+      <c r="H225" s="5" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="9" t="inlineStr">
+        <is>
+          <t>Sacubitril-Valsartan 3Na Complex</t>
+        </is>
+      </c>
+      <c r="B226" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C226" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D226" s="9" t="n"/>
+      <c r="E226" s="5" t="n"/>
+      <c r="F226" s="5" t="n"/>
+      <c r="G226" s="5" t="n"/>
+      <c r="H226" s="5" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="9" t="inlineStr">
+        <is>
+          <t>Saw Palmetto</t>
+        </is>
+      </c>
+      <c r="B227" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D227" s="9" t="n"/>
+      <c r="E227" s="5" t="n"/>
+      <c r="F227" s="5" t="n"/>
+      <c r="G227" s="5" t="n"/>
+      <c r="H227" s="5" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="9" t="inlineStr">
+        <is>
+          <t>Siberian Ginseng</t>
+        </is>
+      </c>
+      <c r="B228" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D228" s="9" t="n"/>
+      <c r="E228" s="5" t="n"/>
+      <c r="F228" s="5" t="n"/>
+      <c r="G228" s="5" t="n"/>
+      <c r="H228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="9" t="inlineStr">
+        <is>
+          <t>Silica gel</t>
+        </is>
+      </c>
+      <c r="B229" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C229" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D229" s="9" t="n"/>
+      <c r="E229" s="5" t="n"/>
+      <c r="F229" s="5" t="n"/>
+      <c r="G229" s="5" t="n"/>
+      <c r="H229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="9" t="inlineStr">
+        <is>
+          <t>Silybum Marianum(Milk Thistle)</t>
+        </is>
+      </c>
+      <c r="B230" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C230" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D230" s="9" t="n"/>
+      <c r="E230" s="5" t="n"/>
+      <c r="F230" s="5" t="n"/>
+      <c r="G230" s="5" t="n"/>
+      <c r="H230" s="5" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="9" t="inlineStr">
+        <is>
+          <t>Silymarin</t>
+        </is>
+      </c>
+      <c r="B231" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C231" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D231" s="9" t="n"/>
+      <c r="E231" s="5" t="n"/>
+      <c r="F231" s="5" t="n"/>
+      <c r="G231" s="5" t="n"/>
+      <c r="H231" s="5" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="9" t="inlineStr">
+        <is>
+          <t>Silymarin Extract</t>
+        </is>
+      </c>
+      <c r="B232" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C232" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D232" s="9" t="n"/>
+      <c r="E232" s="5" t="n"/>
+      <c r="F232" s="5" t="n"/>
+      <c r="G232" s="5" t="n"/>
+      <c r="H232" s="5" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="9" t="inlineStr">
+        <is>
+          <t>Sodium algenate</t>
+        </is>
+      </c>
+      <c r="B233" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C233" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D233" s="9" t="n"/>
+      <c r="E233" s="5" t="n"/>
+      <c r="F233" s="5" t="n"/>
+      <c r="G233" s="5" t="n"/>
+      <c r="H233" s="5" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Borate Decahydrate</t>
+        </is>
+      </c>
+      <c r="B234" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C234" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D234" s="9" t="n"/>
+      <c r="E234" s="5" t="n"/>
+      <c r="F234" s="5" t="n"/>
+      <c r="G234" s="5" t="n"/>
+      <c r="H234" s="5" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Carbonate Anhydrous</t>
+        </is>
+      </c>
+      <c r="B235" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C235" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D235" s="9" t="n"/>
+      <c r="E235" s="5" t="n"/>
+      <c r="F235" s="5" t="n"/>
+      <c r="G235" s="5" t="n"/>
+      <c r="H235" s="5" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Croscarmellose</t>
+        </is>
+      </c>
+      <c r="B236" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C236" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D236" s="9" t="n"/>
+      <c r="E236" s="5" t="n"/>
+      <c r="F236" s="5" t="n"/>
+      <c r="G236" s="5" t="n"/>
+      <c r="H236" s="5" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="9" t="inlineStr">
+        <is>
+          <t>Sodium dodecyl Sulfate Ph Eur</t>
+        </is>
+      </c>
+      <c r="B237" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C237" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D237" s="9" t="n"/>
+      <c r="E237" s="5" t="n"/>
+      <c r="F237" s="5" t="n"/>
+      <c r="G237" s="5" t="n"/>
+      <c r="H237" s="5" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Hydroxide granulated</t>
+        </is>
+      </c>
+      <c r="B238" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="n"/>
+      <c r="E238" s="5" t="n"/>
+      <c r="F238" s="5" t="n"/>
+      <c r="G238" s="5" t="n"/>
+      <c r="H238" s="5" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="9" t="inlineStr">
+        <is>
+          <t>Sorbitol Liquid</t>
+        </is>
+      </c>
+      <c r="B239" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D239" s="9" t="n"/>
+      <c r="E239" s="5" t="n"/>
+      <c r="F239" s="5" t="n"/>
+      <c r="G239" s="5" t="n"/>
+      <c r="H239" s="5" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>Sorbitol Liquid-70%</t>
+        </is>
+      </c>
+      <c r="B240" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C240" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D240" s="9" t="n"/>
+      <c r="E240" s="5" t="n"/>
+      <c r="F240" s="5" t="n"/>
+      <c r="G240" s="5" t="n"/>
+      <c r="H240" s="5" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="9" t="inlineStr">
+        <is>
+          <t>Spray Dirid Licorice Extract Powder</t>
+        </is>
+      </c>
+      <c r="B241" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C241" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D241" s="9" t="n"/>
+      <c r="E241" s="5" t="n"/>
+      <c r="F241" s="5" t="n"/>
+      <c r="G241" s="5" t="n"/>
+      <c r="H241" s="5" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="9" t="inlineStr">
+        <is>
+          <t>Strawberry Flavor Liquid</t>
+        </is>
+      </c>
+      <c r="B242" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D242" s="9" t="n"/>
+      <c r="E242" s="5" t="n"/>
+      <c r="F242" s="5" t="n"/>
+      <c r="G242" s="5" t="n"/>
+      <c r="H242" s="5" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="9" t="inlineStr">
+        <is>
+          <t>Sucralose+B650:L650</t>
+        </is>
+      </c>
+      <c r="B243" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C243" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D243" s="9" t="n"/>
+      <c r="E243" s="5" t="n"/>
+      <c r="F243" s="5" t="n"/>
+      <c r="G243" s="5" t="n"/>
+      <c r="H243" s="5" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="9" t="inlineStr">
+        <is>
+          <t>Sugar</t>
+        </is>
+      </c>
+      <c r="B244" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D244" s="9" t="n"/>
+      <c r="E244" s="5" t="n"/>
+      <c r="F244" s="5" t="n"/>
+      <c r="G244" s="5" t="n"/>
+      <c r="H244" s="5" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="9" t="inlineStr">
+        <is>
+          <t>Sweetmint Flavour</t>
+        </is>
+      </c>
+      <c r="B245" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D245" s="9" t="n"/>
+      <c r="E245" s="5" t="n"/>
+      <c r="F245" s="5" t="n"/>
+      <c r="G245" s="5" t="n"/>
+      <c r="H245" s="5" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="9" t="inlineStr">
+        <is>
+          <t>Talc USP</t>
+        </is>
+      </c>
+      <c r="B246" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C246" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D246" s="9" t="n"/>
+      <c r="E246" s="5" t="n"/>
+      <c r="F246" s="5" t="n"/>
+      <c r="G246" s="5" t="n"/>
+      <c r="H246" s="5" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="9" t="inlineStr">
+        <is>
+          <t>Titanium</t>
+        </is>
+      </c>
+      <c r="B247" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C247" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D247" s="9" t="n"/>
+      <c r="E247" s="5" t="n"/>
+      <c r="F247" s="5" t="n"/>
+      <c r="G247" s="5" t="n"/>
+      <c r="H247" s="5" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="9" t="inlineStr">
+        <is>
+          <t>Titriplex</t>
+        </is>
+      </c>
+      <c r="B248" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C248" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D248" s="9" t="n"/>
+      <c r="E248" s="5" t="n"/>
+      <c r="F248" s="5" t="n"/>
+      <c r="G248" s="5" t="n"/>
+      <c r="H248" s="5" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="9" t="inlineStr">
+        <is>
+          <t>Titriplex III</t>
+        </is>
+      </c>
+      <c r="B249" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C249" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D249" s="9" t="n"/>
+      <c r="E249" s="5" t="n"/>
+      <c r="F249" s="5" t="n"/>
+      <c r="G249" s="5" t="n"/>
+      <c r="H249" s="5" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="9" t="inlineStr">
+        <is>
+          <t>Valerian Root Extract</t>
+        </is>
+      </c>
+      <c r="B250" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C250" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="n"/>
+      <c r="E250" s="5" t="n"/>
+      <c r="F250" s="5" t="n"/>
+      <c r="G250" s="5" t="n"/>
+      <c r="H250" s="5" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="9" t="inlineStr">
+        <is>
+          <t>Vanilla Flavor</t>
+        </is>
+      </c>
+      <c r="B251" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C251" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D251" s="9" t="n"/>
+      <c r="E251" s="5" t="n"/>
+      <c r="F251" s="5" t="n"/>
+      <c r="G251" s="5" t="n"/>
+      <c r="H251" s="5" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="9" t="inlineStr">
+        <is>
+          <t>Vanilla Toffee</t>
+        </is>
+      </c>
+      <c r="B252" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C252" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D252" s="9" t="n"/>
+      <c r="E252" s="5" t="n"/>
+      <c r="F252" s="5" t="n"/>
+      <c r="G252" s="5" t="n"/>
+      <c r="H252" s="5" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="9" t="inlineStr">
+        <is>
+          <t>Vericiguat (VCG)</t>
+        </is>
+      </c>
+      <c r="B253" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C253" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D253" s="9" t="n"/>
+      <c r="E253" s="5" t="n"/>
+      <c r="F253" s="5" t="n"/>
+      <c r="G253" s="5" t="n"/>
+      <c r="H253" s="5" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="9" t="inlineStr">
+        <is>
+          <t>Vibegron-WB</t>
+        </is>
+      </c>
+      <c r="B254" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C254" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D254" s="9" t="n"/>
+      <c r="E254" s="5" t="n"/>
+      <c r="F254" s="5" t="n"/>
+      <c r="G254" s="5" t="n"/>
+      <c r="H254" s="5" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin A</t>
+        </is>
+      </c>
+      <c r="B255" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D255" s="9" t="n"/>
+      <c r="E255" s="5" t="n"/>
+      <c r="F255" s="5" t="n"/>
+      <c r="G255" s="5" t="n"/>
+      <c r="H255" s="5" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="9" t="inlineStr">
+        <is>
+          <t>vitamin A Acetate 500 SD CWS/A</t>
+        </is>
+      </c>
+      <c r="B256" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C256" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D256" s="9" t="n"/>
+      <c r="E256" s="5" t="n"/>
+      <c r="F256" s="5" t="n"/>
+      <c r="G256" s="5" t="n"/>
+      <c r="H256" s="5" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin A acetate Powder</t>
+        </is>
+      </c>
+      <c r="B257" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C257" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D257" s="9" t="n"/>
+      <c r="E257" s="5" t="n"/>
+      <c r="F257" s="5" t="n"/>
+      <c r="G257" s="5" t="n"/>
+      <c r="H257" s="5" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin A Powder</t>
+        </is>
+      </c>
+      <c r="B258" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C258" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D258" s="9" t="n"/>
+      <c r="E258" s="5" t="n"/>
+      <c r="F258" s="5" t="n"/>
+      <c r="G258" s="5" t="n"/>
+      <c r="H258" s="5" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin A Powder-50000</t>
+        </is>
+      </c>
+      <c r="B259" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C259" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D259" s="9" t="n"/>
+      <c r="E259" s="5" t="n"/>
+      <c r="F259" s="5" t="n"/>
+      <c r="G259" s="5" t="n"/>
+      <c r="H259" s="5" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin B 6- Food Grade</t>
+        </is>
+      </c>
+      <c r="B260" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C260" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D260" s="9" t="n"/>
+      <c r="E260" s="5" t="n"/>
+      <c r="F260" s="5" t="n"/>
+      <c r="G260" s="5" t="n"/>
+      <c r="H260" s="5" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin B2(Riboflavin</t>
+        </is>
+      </c>
+      <c r="B261" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C261" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D261" s="9" t="n"/>
+      <c r="E261" s="5" t="n"/>
+      <c r="F261" s="5" t="n"/>
+      <c r="G261" s="5" t="n"/>
+      <c r="H261" s="5" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="9" t="inlineStr">
+        <is>
+          <t>VITAMIN C COATED-97.05%</t>
+        </is>
+      </c>
+      <c r="B262" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C262" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D262" s="9" t="n"/>
+      <c r="E262" s="5" t="n"/>
+      <c r="F262" s="5" t="n"/>
+      <c r="G262" s="5" t="n"/>
+      <c r="H262" s="5" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin D3 -100000</t>
+        </is>
+      </c>
+      <c r="B263" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C263" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D263" s="9" t="n"/>
+      <c r="E263" s="5" t="n"/>
+      <c r="F263" s="5" t="n"/>
+      <c r="G263" s="5" t="n"/>
+      <c r="H263" s="5" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin D3 Powder</t>
+        </is>
+      </c>
+      <c r="B264" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C264" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D264" s="9" t="n"/>
+      <c r="E264" s="5" t="n"/>
+      <c r="F264" s="5" t="n"/>
+      <c r="G264" s="5" t="n"/>
+      <c r="H264" s="5" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin K1 5% Powder</t>
+        </is>
+      </c>
+      <c r="B265" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="n"/>
+      <c r="E265" s="5" t="n"/>
+      <c r="F265" s="5" t="n"/>
+      <c r="G265" s="5" t="n"/>
+      <c r="H265" s="5" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin k1-Sample</t>
+        </is>
+      </c>
+      <c r="B266" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C266" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D266" s="9" t="n"/>
+      <c r="E266" s="5" t="n"/>
+      <c r="F266" s="5" t="n"/>
+      <c r="G266" s="5" t="n"/>
+      <c r="H266" s="5" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin k2</t>
+        </is>
+      </c>
+      <c r="B267" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C267" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D267" s="9" t="n"/>
+      <c r="E267" s="5" t="n"/>
+      <c r="F267" s="5" t="n"/>
+      <c r="G267" s="5" t="n"/>
+      <c r="H267" s="5" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="9" t="inlineStr">
+        <is>
+          <t>Vonoprazan Fumarate IH</t>
+        </is>
+      </c>
+      <c r="B268" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C268" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D268" s="9" t="n"/>
+      <c r="E268" s="5" t="n"/>
+      <c r="F268" s="5" t="n"/>
+      <c r="G268" s="5" t="n"/>
+      <c r="H268" s="5" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="9" t="inlineStr">
+        <is>
+          <t>رنگ کارامل</t>
+        </is>
+      </c>
+      <c r="B269" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C269" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D269" s="9" t="n"/>
+      <c r="E269" s="5" t="n"/>
+      <c r="F269" s="5" t="n"/>
+      <c r="G269" s="5" t="n"/>
+      <c r="H269" s="5" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="9" t="inlineStr">
+        <is>
+          <t>شکر دارویی</t>
+        </is>
+      </c>
+      <c r="B270" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C270" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D270" s="9" t="n"/>
+      <c r="E270" s="5" t="n"/>
+      <c r="F270" s="5" t="n"/>
+      <c r="G270" s="5" t="n"/>
+      <c r="H270" s="5" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="9" t="inlineStr">
+        <is>
+          <t>پلی اتیلن گلیکول 4000 (PEG4000)</t>
+        </is>
+      </c>
+      <c r="B271" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C271" s="9" t="inlineStr">
+        <is>
+          <t>Not in study</t>
+        </is>
+      </c>
+      <c r="D271" s="9" t="n"/>
+      <c r="E271" s="5" t="n"/>
+      <c r="F271" s="5" t="n"/>
+      <c r="G271" s="5" t="n"/>
+      <c r="H271" s="5" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="9" t="inlineStr">
+        <is>
+          <t>Betadex Sulfobutyl Ether Sodium</t>
+        </is>
+      </c>
+      <c r="B272" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C272" s="9" t="inlineStr">
+        <is>
+          <t>In Leadtime.xlsx only</t>
+        </is>
+      </c>
+      <c r="D272" s="9" t="n"/>
+      <c r="E272" s="5" t="n"/>
+      <c r="F272" s="5" t="n"/>
+      <c r="G272" s="5" t="n"/>
+      <c r="H272" s="5" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="9" t="inlineStr">
+        <is>
+          <t>Choline Chloride</t>
+        </is>
+      </c>
+      <c r="B273" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C273" s="9" t="inlineStr">
+        <is>
+          <t>In Leadtime.xlsx only</t>
+        </is>
+      </c>
+      <c r="D273" s="9" t="n"/>
+      <c r="E273" s="5" t="n"/>
+      <c r="F273" s="5" t="n"/>
+      <c r="G273" s="5" t="n"/>
+      <c r="H273" s="5" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="9" t="inlineStr">
+        <is>
+          <t>Melatonin</t>
+        </is>
+      </c>
+      <c r="B274" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C274" s="9" t="inlineStr">
+        <is>
+          <t>In Leadtime.xlsx only</t>
+        </is>
+      </c>
+      <c r="D274" s="9" t="n"/>
+      <c r="E274" s="5" t="n"/>
+      <c r="F274" s="5" t="n"/>
+      <c r="G274" s="5" t="n"/>
+      <c r="H274" s="5" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="9" t="inlineStr">
+        <is>
+          <t>Potassium Sorbate</t>
+        </is>
+      </c>
+      <c r="B275" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C275" s="9" t="inlineStr">
+        <is>
+          <t>In Leadtime.xlsx only</t>
+        </is>
+      </c>
+      <c r="D275" s="9" t="n"/>
+      <c r="E275" s="5" t="n"/>
+      <c r="F275" s="5" t="n"/>
+      <c r="G275" s="5" t="n"/>
+      <c r="H275" s="5" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="9" t="inlineStr">
+        <is>
+          <t>Sitagliptin Phosphate Monohydrate</t>
+        </is>
+      </c>
+      <c r="B276" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C276" s="9" t="inlineStr">
+        <is>
+          <t>In Leadtime.xlsx only</t>
+        </is>
+      </c>
+      <c r="D276" s="9" t="n"/>
+      <c r="E276" s="5" t="n"/>
+      <c r="F276" s="5" t="n"/>
+      <c r="G276" s="5" t="n"/>
+      <c r="H276" s="5" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="9" t="inlineStr">
+        <is>
+          <t>Stearic Acid</t>
+        </is>
+      </c>
+      <c r="B277" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C277" s="9" t="inlineStr">
+        <is>
+          <t>In Leadtime.xlsx only</t>
+        </is>
+      </c>
+      <c r="D277" s="9" t="n"/>
+      <c r="E277" s="5" t="n"/>
+      <c r="F277" s="5" t="n"/>
+      <c r="G277" s="5" t="n"/>
+      <c r="H277" s="5" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="9" t="inlineStr">
+        <is>
+          <t>Xanthan Gum(SUPER GELL 6010)</t>
+        </is>
+      </c>
+      <c r="B278" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C278" s="9" t="inlineStr">
+        <is>
+          <t>In Leadtime.xlsx only</t>
+        </is>
+      </c>
+      <c r="D278" s="9" t="n"/>
+      <c r="E278" s="5" t="n"/>
+      <c r="F278" s="5" t="n"/>
+      <c r="G278" s="5" t="n"/>
+      <c r="H278" s="5" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="9" t="inlineStr">
+        <is>
+          <t>Xylitol</t>
+        </is>
+      </c>
+      <c r="B279" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C279" s="9" t="inlineStr">
+        <is>
+          <t>In Leadtime.xlsx only</t>
+        </is>
+      </c>
+      <c r="D279" s="9" t="n"/>
+      <c r="E279" s="5" t="n"/>
+      <c r="F279" s="5" t="n"/>
+      <c r="G279" s="5" t="n"/>
+      <c r="H279" s="5" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="9" t="inlineStr">
+        <is>
+          <t>Acetaminophen</t>
+        </is>
+      </c>
+      <c r="B280" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C280" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D280" s="9" t="inlineStr">
+        <is>
+          <t>Acetaminophen</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="n"/>
+      <c r="F280" s="5" t="n"/>
+      <c r="G280" s="5" t="n"/>
+      <c r="H280" s="5" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="9" t="inlineStr">
+        <is>
+          <t>Alcohol 96% (Ethanol)</t>
+        </is>
+      </c>
+      <c r="B281" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C281" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D281" s="9" t="inlineStr">
+        <is>
+          <t>Ethanol 96%</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="n"/>
+      <c r="F281" s="5" t="n"/>
+      <c r="G281" s="5" t="n"/>
+      <c r="H281" s="5" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="9" t="inlineStr">
+        <is>
+          <t>Allura Red</t>
+        </is>
+      </c>
+      <c r="B282" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C282" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D282" s="9" t="inlineStr">
+        <is>
+          <t>Allura Red</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="n"/>
+      <c r="F282" s="5" t="n"/>
+      <c r="G282" s="5" t="n"/>
+      <c r="H282" s="5" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="9" t="inlineStr">
+        <is>
+          <t>Amlodipine Besylate</t>
+        </is>
+      </c>
+      <c r="B283" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C283" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D283" s="9" t="inlineStr">
+        <is>
+          <t>Amlodipine Besylate</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="n"/>
+      <c r="F283" s="5" t="n"/>
+      <c r="G283" s="5" t="n"/>
+      <c r="H283" s="5" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="9" t="inlineStr">
+        <is>
+          <t>Apium Graveolens</t>
+        </is>
+      </c>
+      <c r="B284" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C284" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D284" s="9" t="inlineStr">
+        <is>
+          <t>Apium Graveolens Seed Dry Extract 6:1</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="n"/>
+      <c r="F284" s="5" t="n"/>
+      <c r="G284" s="5" t="n"/>
+      <c r="H284" s="5" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="9" t="inlineStr">
+        <is>
+          <t>Apple Green</t>
+        </is>
+      </c>
+      <c r="B285" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C285" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D285" s="9" t="inlineStr">
+        <is>
+          <t>Apple Green Color</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="n"/>
+      <c r="F285" s="5" t="n"/>
+      <c r="G285" s="5" t="n"/>
+      <c r="H285" s="5" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="9" t="inlineStr">
+        <is>
+          <t>Artichoke dry extract</t>
+        </is>
+      </c>
+      <c r="B286" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C286" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D286" s="9" t="inlineStr">
+        <is>
+          <t>Artichoke Dry Extract 25:1</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="n"/>
+      <c r="F286" s="5" t="n"/>
+      <c r="G286" s="5" t="n"/>
+      <c r="H286" s="5" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="9" t="inlineStr">
+        <is>
+          <t>Ascorbic Acid</t>
+        </is>
+      </c>
+      <c r="B287" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C287" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D287" s="9" t="inlineStr">
+        <is>
+          <t>Ascorbic Acid (Vitamin C)</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="n"/>
+      <c r="F287" s="5" t="n"/>
+      <c r="G287" s="5" t="n"/>
+      <c r="H287" s="5" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="9" t="inlineStr">
+        <is>
+          <t>Ascorbic Acid-Coated -97</t>
+        </is>
+      </c>
+      <c r="B288" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C288" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D288" s="9" t="inlineStr">
+        <is>
+          <t>Ascorbic Acid Coated 97%</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="n"/>
+      <c r="F288" s="5" t="n"/>
+      <c r="G288" s="5" t="n"/>
+      <c r="H288" s="5" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="9" t="inlineStr">
+        <is>
+          <t>Bempedoic Acid</t>
+        </is>
+      </c>
+      <c r="B289" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C289" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D289" s="9" t="inlineStr">
+        <is>
+          <t>Bempedoic Acid</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="n"/>
+      <c r="F289" s="5" t="n"/>
+      <c r="G289" s="5" t="n"/>
+      <c r="H289" s="5" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="9" t="inlineStr">
+        <is>
+          <t>Beta-Carotene-10%</t>
+        </is>
+      </c>
+      <c r="B290" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C290" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D290" s="9" t="inlineStr">
+        <is>
+          <t>Beta-Carotene</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="n"/>
+      <c r="F290" s="5" t="n"/>
+      <c r="G290" s="5" t="n"/>
+      <c r="H290" s="5" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="9" t="inlineStr">
+        <is>
+          <t>Biotin</t>
+        </is>
+      </c>
+      <c r="B291" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C291" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D291" s="9" t="inlineStr">
+        <is>
+          <t>Biotin (Vitamin B7)</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="n"/>
+      <c r="F291" s="5" t="n"/>
+      <c r="G291" s="5" t="n"/>
+      <c r="H291" s="5" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="9" t="inlineStr">
+        <is>
+          <t>Black Iron Oxide</t>
+        </is>
+      </c>
+      <c r="B292" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C292" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D292" s="9" t="inlineStr">
+        <is>
+          <t>Ferric Oxide Black</t>
+        </is>
+      </c>
+      <c r="E292" s="5" t="n"/>
+      <c r="F292" s="5" t="n"/>
+      <c r="G292" s="5" t="n"/>
+      <c r="H292" s="5" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="9" t="inlineStr">
+        <is>
+          <t>BRILLIANT BLUE</t>
+        </is>
+      </c>
+      <c r="B293" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C293" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D293" s="9" t="inlineStr">
+        <is>
+          <t>Brilliant Blue</t>
+        </is>
+      </c>
+      <c r="E293" s="5" t="n"/>
+      <c r="F293" s="5" t="n"/>
+      <c r="G293" s="5" t="n"/>
+      <c r="H293" s="5" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="9" t="inlineStr">
+        <is>
+          <t>Caffeine</t>
+        </is>
+      </c>
+      <c r="B294" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C294" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D294" s="9" t="inlineStr">
+        <is>
+          <t>Caffeine (Base)</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="n"/>
+      <c r="F294" s="5" t="n"/>
+      <c r="G294" s="5" t="n"/>
+      <c r="H294" s="5" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Carbonate (Heavy)</t>
+        </is>
+      </c>
+      <c r="B295" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C295" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D295" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Carbonate</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="n"/>
+      <c r="F295" s="5" t="n"/>
+      <c r="G295" s="5" t="n"/>
+      <c r="H295" s="5" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Carbonate Heavy</t>
+        </is>
+      </c>
+      <c r="B296" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C296" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D296" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Carbonate Heavy</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="n"/>
+      <c r="F296" s="5" t="n"/>
+      <c r="G296" s="5" t="n"/>
+      <c r="H296" s="5" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Pantothenate (Vitamin B5)</t>
+        </is>
+      </c>
+      <c r="B297" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C297" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D297" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Pantothenate (Vitamin B5)</t>
+        </is>
+      </c>
+      <c r="E297" s="5" t="n"/>
+      <c r="F297" s="5" t="n"/>
+      <c r="G297" s="5" t="n"/>
+      <c r="H297" s="5" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="9" t="inlineStr">
+        <is>
+          <t>Caramel Colour</t>
+        </is>
+      </c>
+      <c r="B298" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C298" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D298" s="9" t="inlineStr">
+        <is>
+          <t>Caramel Colour</t>
+        </is>
+      </c>
+      <c r="E298" s="5" t="n"/>
+      <c r="F298" s="5" t="n"/>
+      <c r="G298" s="5" t="n"/>
+      <c r="H298" s="5" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="9" t="inlineStr">
+        <is>
+          <t>Choline bitartrate</t>
+        </is>
+      </c>
+      <c r="B299" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C299" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D299" s="9" t="inlineStr">
+        <is>
+          <t>Choline Bitartrate</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="n"/>
+      <c r="F299" s="5" t="n"/>
+      <c r="G299" s="5" t="n"/>
+      <c r="H299" s="5" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="9" t="inlineStr">
+        <is>
+          <t>Chromium Picolinate</t>
+        </is>
+      </c>
+      <c r="B300" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C300" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D300" s="9" t="inlineStr">
+        <is>
+          <t>Chromium Picolinate</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="n"/>
+      <c r="F300" s="5" t="n"/>
+      <c r="G300" s="5" t="n"/>
+      <c r="H300" s="5" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="9" t="inlineStr">
+        <is>
+          <t>Citicoline Sodium</t>
+        </is>
+      </c>
+      <c r="B301" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C301" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D301" s="9" t="inlineStr">
+        <is>
+          <t>Citicoline Sodium</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="n"/>
+      <c r="F301" s="5" t="n"/>
+      <c r="G301" s="5" t="n"/>
+      <c r="H301" s="5" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="9" t="inlineStr">
+        <is>
+          <t>Citric acid Anhydrous</t>
+        </is>
+      </c>
+      <c r="B302" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C302" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D302" s="9" t="inlineStr">
+        <is>
+          <t>Citric Acid Anhydrous</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="n"/>
+      <c r="F302" s="5" t="n"/>
+      <c r="G302" s="5" t="n"/>
+      <c r="H302" s="5" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="9" t="inlineStr">
+        <is>
+          <t>Cola Flavour</t>
+        </is>
+      </c>
+      <c r="B303" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C303" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D303" s="9" t="inlineStr">
+        <is>
+          <t>Cola Flavour</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="n"/>
+      <c r="F303" s="5" t="n"/>
+      <c r="G303" s="5" t="n"/>
+      <c r="H303" s="5" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="9" t="inlineStr">
+        <is>
+          <t>Colloidal Silicon Dioxide</t>
+        </is>
+      </c>
+      <c r="B304" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C304" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D304" s="9" t="inlineStr">
+        <is>
+          <t>Colloidal Silicon Dioxide</t>
+        </is>
+      </c>
+      <c r="E304" s="5" t="n"/>
+      <c r="F304" s="5" t="n"/>
+      <c r="G304" s="5" t="n"/>
+      <c r="H304" s="5" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="9" t="inlineStr">
+        <is>
+          <t>Copper Gluconate</t>
+        </is>
+      </c>
+      <c r="B305" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C305" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D305" s="9" t="inlineStr">
+        <is>
+          <t>Copper Gluconate</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="n"/>
+      <c r="F305" s="5" t="n"/>
+      <c r="G305" s="5" t="n"/>
+      <c r="H305" s="5" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="9" t="inlineStr">
+        <is>
+          <t>Corn Starch</t>
+        </is>
+      </c>
+      <c r="B306" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C306" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D306" s="9" t="inlineStr">
+        <is>
+          <t>Corn Starch</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="n"/>
+      <c r="F306" s="5" t="n"/>
+      <c r="G306" s="5" t="n"/>
+      <c r="H306" s="5" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="9" t="inlineStr">
+        <is>
+          <t>Croscarmellose Sodium</t>
+        </is>
+      </c>
+      <c r="B307" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C307" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D307" s="9" t="inlineStr">
+        <is>
+          <t>Croscarmellose Sodium</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="n"/>
+      <c r="F307" s="5" t="n"/>
+      <c r="G307" s="5" t="n"/>
+      <c r="H307" s="5" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="9" t="inlineStr">
+        <is>
+          <t>Crospovidone</t>
+        </is>
+      </c>
+      <c r="B308" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C308" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D308" s="9" t="inlineStr">
+        <is>
+          <t>Crospovidone</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="n"/>
+      <c r="F308" s="5" t="n"/>
+      <c r="G308" s="5" t="n"/>
+      <c r="H308" s="5" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="9" t="inlineStr">
+        <is>
+          <t>Crospovidone- Type A</t>
+        </is>
+      </c>
+      <c r="B309" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C309" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D309" s="9" t="inlineStr">
+        <is>
+          <t>Crospovidone</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="n"/>
+      <c r="F309" s="5" t="n"/>
+      <c r="G309" s="5" t="n"/>
+      <c r="H309" s="5" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="9" t="inlineStr">
+        <is>
+          <t>Crosscarmellose Sodium</t>
+        </is>
+      </c>
+      <c r="B310" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C310" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D310" s="9" t="inlineStr">
+        <is>
+          <t>Croscarmellose Sodium</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="n"/>
+      <c r="F310" s="5" t="n"/>
+      <c r="G310" s="5" t="n"/>
+      <c r="H310" s="5" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="9" t="inlineStr">
+        <is>
+          <t>Cyanocobalamin</t>
+        </is>
+      </c>
+      <c r="B311" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C311" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D311" s="9" t="inlineStr">
+        <is>
+          <t>Cyanocobalamin (Vitamin B12)</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="n"/>
+      <c r="F311" s="5" t="n"/>
+      <c r="G311" s="5" t="n"/>
+      <c r="H311" s="5" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="9" t="inlineStr">
+        <is>
+          <t>D-Biotin</t>
+        </is>
+      </c>
+      <c r="B312" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C312" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D312" s="9" t="inlineStr">
+        <is>
+          <t>Biotin (Vitamin B7)</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="n"/>
+      <c r="F312" s="5" t="n"/>
+      <c r="G312" s="5" t="n"/>
+      <c r="H312" s="5" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="9" t="inlineStr">
+        <is>
+          <t>Dicalcium Phosphate Anhydrous</t>
+        </is>
+      </c>
+      <c r="B313" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C313" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D313" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Hydrogen Phosphate (Dicalcium Phosphate)</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="n"/>
+      <c r="F313" s="5" t="n"/>
+      <c r="G313" s="5" t="n"/>
+      <c r="H313" s="5" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="9" t="inlineStr">
+        <is>
+          <t>Diphenhydramine HCL</t>
+        </is>
+      </c>
+      <c r="B314" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C314" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D314" s="9" t="inlineStr">
+        <is>
+          <t>Diphenhydramine HCl</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="n"/>
+      <c r="F314" s="5" t="n"/>
+      <c r="G314" s="5" t="n"/>
+      <c r="H314" s="5" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="9" t="inlineStr">
+        <is>
+          <t>Empagliflozin</t>
+        </is>
+      </c>
+      <c r="B315" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C315" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D315" s="9" t="inlineStr">
+        <is>
+          <t>Empagliflozin</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="n"/>
+      <c r="F315" s="5" t="n"/>
+      <c r="G315" s="5" t="n"/>
+      <c r="H315" s="5" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="9" t="inlineStr">
+        <is>
+          <t>ERYTHROSINE</t>
+        </is>
+      </c>
+      <c r="B316" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C316" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D316" s="9" t="inlineStr">
+        <is>
+          <t>Erythrosine Pink</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="n"/>
+      <c r="F316" s="5" t="n"/>
+      <c r="G316" s="5" t="n"/>
+      <c r="H316" s="5" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="9" t="inlineStr">
+        <is>
+          <t>Ethanol</t>
+        </is>
+      </c>
+      <c r="B317" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C317" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D317" s="9" t="inlineStr">
+        <is>
+          <t>Ethanol (% not stated)</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="n"/>
+      <c r="F317" s="5" t="n"/>
+      <c r="G317" s="5" t="n"/>
+      <c r="H317" s="5" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="9" t="inlineStr">
+        <is>
+          <t>Ethanol 96%</t>
+        </is>
+      </c>
+      <c r="B318" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C318" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D318" s="9" t="inlineStr">
+        <is>
+          <t>Ethanol 96%</t>
+        </is>
+      </c>
+      <c r="E318" s="5" t="n"/>
+      <c r="F318" s="5" t="n"/>
+      <c r="G318" s="5" t="n"/>
+      <c r="H318" s="5" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="9" t="inlineStr">
+        <is>
+          <t>Exacol Brown</t>
+        </is>
+      </c>
+      <c r="B319" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C319" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D319" s="9" t="inlineStr">
+        <is>
+          <t>Exacol Brown HT</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="n"/>
+      <c r="F319" s="5" t="n"/>
+      <c r="G319" s="5" t="n"/>
+      <c r="H319" s="5" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="9" t="inlineStr">
+        <is>
+          <t>Ezetimibe</t>
+        </is>
+      </c>
+      <c r="B320" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C320" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D320" s="9" t="inlineStr">
+        <is>
+          <t>Ezetimibe</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="n"/>
+      <c r="F320" s="5" t="n"/>
+      <c r="G320" s="5" t="n"/>
+      <c r="H320" s="5" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="9" t="inlineStr">
+        <is>
+          <t>Ferrous Bisglycinate</t>
+        </is>
+      </c>
+      <c r="B321" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C321" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D321" s="9" t="inlineStr">
+        <is>
+          <t>Ferrous Bisglycinate</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="n"/>
+      <c r="F321" s="5" t="n"/>
+      <c r="G321" s="5" t="n"/>
+      <c r="H321" s="5" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="9" t="inlineStr">
+        <is>
+          <t>Ferrous Fumarate</t>
+        </is>
+      </c>
+      <c r="B322" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C322" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D322" s="9" t="inlineStr">
+        <is>
+          <t>Ferrous Fumarate</t>
+        </is>
+      </c>
+      <c r="E322" s="5" t="n"/>
+      <c r="F322" s="5" t="n"/>
+      <c r="G322" s="5" t="n"/>
+      <c r="H322" s="5" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="9" t="inlineStr">
+        <is>
+          <t>Finerenone</t>
+        </is>
+      </c>
+      <c r="B323" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C323" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D323" s="9" t="inlineStr">
+        <is>
+          <t>Finerenone</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="n"/>
+      <c r="F323" s="5" t="n"/>
+      <c r="G323" s="5" t="n"/>
+      <c r="H323" s="5" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="9" t="inlineStr">
+        <is>
+          <t>Folic Acid</t>
+        </is>
+      </c>
+      <c r="B324" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C324" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D324" s="9" t="inlineStr">
+        <is>
+          <t>Folic Acid (Vitamin B9)</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="n"/>
+      <c r="F324" s="5" t="n"/>
+      <c r="G324" s="5" t="n"/>
+      <c r="H324" s="5" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="9" t="inlineStr">
+        <is>
+          <t>Hard Gelatin Capsule (Brown)</t>
+        </is>
+      </c>
+      <c r="B325" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C325" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D325" s="9" t="inlineStr">
+        <is>
+          <t>Hard Gelatin Capsule</t>
+        </is>
+      </c>
+      <c r="E325" s="5" t="n"/>
+      <c r="F325" s="5" t="n"/>
+      <c r="G325" s="5" t="n"/>
+      <c r="H325" s="5" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="9" t="inlineStr">
+        <is>
+          <t>Heavy Magnesium Oxide</t>
+        </is>
+      </c>
+      <c r="B326" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C326" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D326" s="9" t="inlineStr">
+        <is>
+          <t>Magnesium Oxide Heavy</t>
+        </is>
+      </c>
+      <c r="E326" s="5" t="n"/>
+      <c r="F326" s="5" t="n"/>
+      <c r="G326" s="5" t="n"/>
+      <c r="H326" s="5" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="9" t="inlineStr">
+        <is>
+          <t>HPMC K15M</t>
+        </is>
+      </c>
+      <c r="B327" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C327" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D327" s="9" t="inlineStr">
+        <is>
+          <t>HPMC K15M (15,000 cps CR)</t>
+        </is>
+      </c>
+      <c r="E327" s="5" t="n"/>
+      <c r="F327" s="5" t="n"/>
+      <c r="G327" s="5" t="n"/>
+      <c r="H327" s="5" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="9" t="inlineStr">
+        <is>
+          <t>Hydrochlorothiazide</t>
+        </is>
+      </c>
+      <c r="B328" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C328" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D328" s="9" t="inlineStr">
+        <is>
+          <t>Hydrochlorothiazide</t>
+        </is>
+      </c>
+      <c r="E328" s="5" t="n"/>
+      <c r="F328" s="5" t="n"/>
+      <c r="G328" s="5" t="n"/>
+      <c r="H328" s="5" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="9" t="inlineStr">
+        <is>
+          <t>Hydroxy Propyl Methyl Cellulose</t>
+        </is>
+      </c>
+      <c r="B329" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C329" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D329" s="9" t="inlineStr">
+        <is>
+          <t>HPMC 6cps (Hypromellose)</t>
+        </is>
+      </c>
+      <c r="E329" s="5" t="n"/>
+      <c r="F329" s="5" t="n"/>
+      <c r="G329" s="5" t="n"/>
+      <c r="H329" s="5" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="9" t="inlineStr">
+        <is>
+          <t>HYDROXY PROPYL METHYL CELLULOSE-K4M</t>
+        </is>
+      </c>
+      <c r="B330" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C330" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D330" s="9" t="inlineStr">
+        <is>
+          <t>HPMC K4M</t>
+        </is>
+      </c>
+      <c r="E330" s="5" t="n"/>
+      <c r="F330" s="5" t="n"/>
+      <c r="G330" s="5" t="n"/>
+      <c r="H330" s="5" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="9" t="inlineStr">
+        <is>
+          <t>Inositol</t>
+        </is>
+      </c>
+      <c r="B331" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C331" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D331" s="9" t="inlineStr">
+        <is>
+          <t>Inositol (Vitamin B8)</t>
+        </is>
+      </c>
+      <c r="E331" s="5" t="n"/>
+      <c r="F331" s="5" t="n"/>
+      <c r="G331" s="5" t="n"/>
+      <c r="H331" s="5" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="9" t="inlineStr">
+        <is>
+          <t>L-Arginine</t>
+        </is>
+      </c>
+      <c r="B332" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C332" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D332" s="9" t="inlineStr">
+        <is>
+          <t>L-Arginine</t>
+        </is>
+      </c>
+      <c r="E332" s="5" t="n"/>
+      <c r="F332" s="5" t="n"/>
+      <c r="G332" s="5" t="n"/>
+      <c r="H332" s="5" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="9" t="inlineStr">
+        <is>
+          <t>L-Cystine</t>
+        </is>
+      </c>
+      <c r="B333" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C333" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D333" s="9" t="inlineStr">
+        <is>
+          <t>L-Cystine</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="n"/>
+      <c r="F333" s="5" t="n"/>
+      <c r="G333" s="5" t="n"/>
+      <c r="H333" s="5" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="9" t="inlineStr">
+        <is>
+          <t>L-Methionine</t>
+        </is>
+      </c>
+      <c r="B334" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C334" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D334" s="9" t="inlineStr">
+        <is>
+          <t>Methionine</t>
+        </is>
+      </c>
+      <c r="E334" s="5" t="n"/>
+      <c r="F334" s="5" t="n"/>
+      <c r="G334" s="5" t="n"/>
+      <c r="H334" s="5" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="9" t="inlineStr">
+        <is>
+          <t>Lactose Monohydrate Mesh-80</t>
+        </is>
+      </c>
+      <c r="B335" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C335" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D335" s="9" t="inlineStr">
+        <is>
+          <t>Lactose Monohydrate</t>
+        </is>
+      </c>
+      <c r="E335" s="5" t="n"/>
+      <c r="F335" s="5" t="n"/>
+      <c r="G335" s="5" t="n"/>
+      <c r="H335" s="5" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="9" t="inlineStr">
+        <is>
+          <t>Lemon Flavour</t>
+        </is>
+      </c>
+      <c r="B336" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C336" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D336" s="9" t="inlineStr">
+        <is>
+          <t>Lemon Flavour</t>
+        </is>
+      </c>
+      <c r="E336" s="5" t="n"/>
+      <c r="F336" s="5" t="n"/>
+      <c r="G336" s="5" t="n"/>
+      <c r="H336" s="5" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="9" t="inlineStr">
+        <is>
+          <t>Linagliptin</t>
+        </is>
+      </c>
+      <c r="B337" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C337" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D337" s="9" t="inlineStr">
+        <is>
+          <t>Linagliptin</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="n"/>
+      <c r="F337" s="5" t="n"/>
+      <c r="G337" s="5" t="n"/>
+      <c r="H337" s="5" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="9" t="inlineStr">
+        <is>
+          <t>Magnesium Oxide heavy</t>
+        </is>
+      </c>
+      <c r="B338" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C338" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D338" s="9" t="inlineStr">
+        <is>
+          <t>Magnesium Oxide Heavy</t>
+        </is>
+      </c>
+      <c r="E338" s="5" t="n"/>
+      <c r="F338" s="5" t="n"/>
+      <c r="G338" s="5" t="n"/>
+      <c r="H338" s="5" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="9" t="inlineStr">
+        <is>
+          <t>Magnesium Stearate</t>
+        </is>
+      </c>
+      <c r="B339" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C339" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D339" s="9" t="inlineStr">
+        <is>
+          <t>Magnesium Stearate</t>
+        </is>
+      </c>
+      <c r="E339" s="5" t="n"/>
+      <c r="F339" s="5" t="n"/>
+      <c r="G339" s="5" t="n"/>
+      <c r="H339" s="5" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="9" t="inlineStr">
+        <is>
+          <t>Maltodextrin</t>
+        </is>
+      </c>
+      <c r="B340" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C340" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D340" s="9" t="inlineStr">
+        <is>
+          <t>Maltodextrin</t>
+        </is>
+      </c>
+      <c r="E340" s="5" t="n"/>
+      <c r="F340" s="5" t="n"/>
+      <c r="G340" s="5" t="n"/>
+      <c r="H340" s="5" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="9" t="inlineStr">
+        <is>
+          <t>Manganese Sulfate Monohydrate</t>
+        </is>
+      </c>
+      <c r="B341" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C341" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D341" s="9" t="inlineStr">
+        <is>
+          <t>Manganese Sulfate Monohydrate</t>
+        </is>
+      </c>
+      <c r="E341" s="5" t="n"/>
+      <c r="F341" s="5" t="n"/>
+      <c r="G341" s="5" t="n"/>
+      <c r="H341" s="5" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="9" t="inlineStr">
+        <is>
+          <t>Mannitol</t>
+        </is>
+      </c>
+      <c r="B342" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C342" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D342" s="9" t="inlineStr">
+        <is>
+          <t>Mannitol</t>
+        </is>
+      </c>
+      <c r="E342" s="5" t="n"/>
+      <c r="F342" s="5" t="n"/>
+      <c r="G342" s="5" t="n"/>
+      <c r="H342" s="5" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="9" t="inlineStr">
+        <is>
+          <t>Meglumine</t>
+        </is>
+      </c>
+      <c r="B343" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C343" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D343" s="9" t="inlineStr">
+        <is>
+          <t>Meglumine</t>
+        </is>
+      </c>
+      <c r="E343" s="5" t="n"/>
+      <c r="F343" s="5" t="n"/>
+      <c r="G343" s="5" t="n"/>
+      <c r="H343" s="5" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="9" t="inlineStr">
+        <is>
+          <t>Metformin</t>
+        </is>
+      </c>
+      <c r="B344" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C344" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D344" s="9" t="inlineStr">
+        <is>
+          <t>Metformin Hydrochloride</t>
+        </is>
+      </c>
+      <c r="E344" s="5" t="n"/>
+      <c r="F344" s="5" t="n"/>
+      <c r="G344" s="5" t="n"/>
+      <c r="H344" s="5" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="9" t="inlineStr">
+        <is>
+          <t>Metformin Hydrochloride</t>
+        </is>
+      </c>
+      <c r="B345" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C345" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D345" s="9" t="inlineStr">
+        <is>
+          <t>Metformin Hydrochloride</t>
+        </is>
+      </c>
+      <c r="E345" s="5" t="n"/>
+      <c r="F345" s="5" t="n"/>
+      <c r="G345" s="5" t="n"/>
+      <c r="H345" s="5" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="9" t="inlineStr">
+        <is>
+          <t>Methyl Paraben</t>
+        </is>
+      </c>
+      <c r="B346" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C346" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D346" s="9" t="inlineStr">
+        <is>
+          <t>Methyl Paraben</t>
+        </is>
+      </c>
+      <c r="E346" s="5" t="n"/>
+      <c r="F346" s="5" t="n"/>
+      <c r="G346" s="5" t="n"/>
+      <c r="H346" s="5" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="9" t="inlineStr">
+        <is>
+          <t>Methyl Sulphonyl Methane</t>
+        </is>
+      </c>
+      <c r="B347" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C347" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D347" s="9" t="inlineStr">
+        <is>
+          <t>Methyl Sulphonyl Methane (MSM)</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="n"/>
+      <c r="F347" s="5" t="n"/>
+      <c r="G347" s="5" t="n"/>
+      <c r="H347" s="5" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline Cellulose</t>
+        </is>
+      </c>
+      <c r="B348" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C348" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D348" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline Cellulose PH 101</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="n"/>
+      <c r="F348" s="5" t="n"/>
+      <c r="G348" s="5" t="n"/>
+      <c r="H348" s="5" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline Cellulose 101</t>
+        </is>
+      </c>
+      <c r="B349" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C349" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D349" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline Cellulose PH 101</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="n"/>
+      <c r="F349" s="5" t="n"/>
+      <c r="G349" s="5" t="n"/>
+      <c r="H349" s="5" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline Cellulose 102</t>
+        </is>
+      </c>
+      <c r="B350" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C350" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D350" s="9" t="inlineStr">
+        <is>
+          <t>Microcrystalline Cellulose PH 102</t>
+        </is>
+      </c>
+      <c r="E350" s="5" t="n"/>
+      <c r="F350" s="5" t="n"/>
+      <c r="G350" s="5" t="n"/>
+      <c r="H350" s="5" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="9" t="inlineStr">
+        <is>
+          <t>Mint Flavour (Powder)</t>
+        </is>
+      </c>
+      <c r="B351" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C351" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D351" s="9" t="inlineStr">
+        <is>
+          <t>Mint Flavour</t>
+        </is>
+      </c>
+      <c r="E351" s="5" t="n"/>
+      <c r="F351" s="5" t="n"/>
+      <c r="G351" s="5" t="n"/>
+      <c r="H351" s="5" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="9" t="inlineStr">
+        <is>
+          <t>Naproxen</t>
+        </is>
+      </c>
+      <c r="B352" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C352" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D352" s="9" t="inlineStr">
+        <is>
+          <t>Naproxen</t>
+        </is>
+      </c>
+      <c r="E352" s="5" t="n"/>
+      <c r="F352" s="5" t="n"/>
+      <c r="G352" s="5" t="n"/>
+      <c r="H352" s="5" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="9" t="inlineStr">
+        <is>
+          <t>Neotame</t>
+        </is>
+      </c>
+      <c r="B353" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C353" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D353" s="9" t="inlineStr">
+        <is>
+          <t>Neotame</t>
+        </is>
+      </c>
+      <c r="E353" s="5" t="n"/>
+      <c r="F353" s="5" t="n"/>
+      <c r="G353" s="5" t="n"/>
+      <c r="H353" s="5" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="9" t="inlineStr">
+        <is>
+          <t>Nicotinamide (Vitamin B3)</t>
+        </is>
+      </c>
+      <c r="B354" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C354" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D354" s="9" t="inlineStr">
+        <is>
+          <t>Nicotinamide (Vitamin B3)</t>
+        </is>
+      </c>
+      <c r="E354" s="5" t="n"/>
+      <c r="F354" s="5" t="n"/>
+      <c r="G354" s="5" t="n"/>
+      <c r="H354" s="5" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="9" t="inlineStr">
+        <is>
+          <t>PEG 4000</t>
+        </is>
+      </c>
+      <c r="B355" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C355" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D355" s="9" t="inlineStr">
+        <is>
+          <t>Polyethylene Glycol 4000 (PEG 4000)</t>
+        </is>
+      </c>
+      <c r="E355" s="5" t="n"/>
+      <c r="F355" s="5" t="n"/>
+      <c r="G355" s="5" t="n"/>
+      <c r="H355" s="5" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="9" t="inlineStr">
+        <is>
+          <t>Phenylethyl Alcohol</t>
+        </is>
+      </c>
+      <c r="B356" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C356" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D356" s="9" t="inlineStr">
+        <is>
+          <t>Phenylethyl Alcohol</t>
+        </is>
+      </c>
+      <c r="E356" s="5" t="n"/>
+      <c r="F356" s="5" t="n"/>
+      <c r="G356" s="5" t="n"/>
+      <c r="H356" s="5" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="9" t="inlineStr">
+        <is>
+          <t>Polyethylene Glycol 4000</t>
+        </is>
+      </c>
+      <c r="B357" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C357" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D357" s="9" t="inlineStr">
+        <is>
+          <t>Polyethylene Glycol 4000 (PEG 4000)</t>
+        </is>
+      </c>
+      <c r="E357" s="5" t="n"/>
+      <c r="F357" s="5" t="n"/>
+      <c r="G357" s="5" t="n"/>
+      <c r="H357" s="5" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="9" t="inlineStr">
+        <is>
+          <t>Polysorbate 80</t>
+        </is>
+      </c>
+      <c r="B358" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C358" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D358" s="9" t="inlineStr">
+        <is>
+          <t>Polysorbate 80</t>
+        </is>
+      </c>
+      <c r="E358" s="5" t="n"/>
+      <c r="F358" s="5" t="n"/>
+      <c r="G358" s="5" t="n"/>
+      <c r="H358" s="5" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="9" t="inlineStr">
+        <is>
+          <t>Potassium Iodide</t>
+        </is>
+      </c>
+      <c r="B359" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C359" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D359" s="9" t="inlineStr">
+        <is>
+          <t>Potassium Iodide</t>
+        </is>
+      </c>
+      <c r="E359" s="5" t="n"/>
+      <c r="F359" s="5" t="n"/>
+      <c r="G359" s="5" t="n"/>
+      <c r="H359" s="5" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="9" t="inlineStr">
+        <is>
+          <t>Povidone K30</t>
+        </is>
+      </c>
+      <c r="B360" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C360" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D360" s="9" t="inlineStr">
+        <is>
+          <t>PVP K30</t>
+        </is>
+      </c>
+      <c r="E360" s="5" t="n"/>
+      <c r="F360" s="5" t="n"/>
+      <c r="G360" s="5" t="n"/>
+      <c r="H360" s="5" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="9" t="inlineStr">
+        <is>
+          <t>Propyl Paraben</t>
+        </is>
+      </c>
+      <c r="B361" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C361" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D361" s="9" t="inlineStr">
+        <is>
+          <t>Propyl Paraben</t>
+        </is>
+      </c>
+      <c r="E361" s="5" t="n"/>
+      <c r="F361" s="5" t="n"/>
+      <c r="G361" s="5" t="n"/>
+      <c r="H361" s="5" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="9" t="inlineStr">
+        <is>
+          <t>Propylene Glycol</t>
+        </is>
+      </c>
+      <c r="B362" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C362" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D362" s="9" t="inlineStr">
+        <is>
+          <t>Propylene Glycol</t>
+        </is>
+      </c>
+      <c r="E362" s="5" t="n"/>
+      <c r="F362" s="5" t="n"/>
+      <c r="G362" s="5" t="n"/>
+      <c r="H362" s="5" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="9" t="inlineStr">
+        <is>
+          <t>Prucalopride Succinate</t>
+        </is>
+      </c>
+      <c r="B363" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C363" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D363" s="9" t="inlineStr">
+        <is>
+          <t>Prucalopride Succinate</t>
+        </is>
+      </c>
+      <c r="E363" s="5" t="n"/>
+      <c r="F363" s="5" t="n"/>
+      <c r="G363" s="5" t="n"/>
+      <c r="H363" s="5" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="9" t="inlineStr">
+        <is>
+          <t>Pyridoxin Hydrochloride (Vitamin B6)</t>
+        </is>
+      </c>
+      <c r="B364" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C364" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D364" s="9" t="inlineStr">
+        <is>
+          <t>Pyridoxine Hydrochloride (Vitamin B6)</t>
+        </is>
+      </c>
+      <c r="E364" s="5" t="n"/>
+      <c r="F364" s="5" t="n"/>
+      <c r="G364" s="5" t="n"/>
+      <c r="H364" s="5" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="9" t="inlineStr">
+        <is>
+          <t>Pyridoxine Hydrochloride(Vitamin B6)</t>
+        </is>
+      </c>
+      <c r="B365" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C365" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D365" s="9" t="inlineStr">
+        <is>
+          <t>Pyridoxine Hydrochloride (Vitamin B6)</t>
+        </is>
+      </c>
+      <c r="E365" s="5" t="n"/>
+      <c r="F365" s="5" t="n"/>
+      <c r="G365" s="5" t="n"/>
+      <c r="H365" s="5" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="9" t="inlineStr">
+        <is>
+          <t>Ranolazine</t>
+        </is>
+      </c>
+      <c r="B366" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C366" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D366" s="9" t="inlineStr">
+        <is>
+          <t>Ranolazine</t>
+        </is>
+      </c>
+      <c r="E366" s="5" t="n"/>
+      <c r="F366" s="5" t="n"/>
+      <c r="G366" s="5" t="n"/>
+      <c r="H366" s="5" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="9" t="inlineStr">
+        <is>
+          <t>RED IRON OXIDE</t>
+        </is>
+      </c>
+      <c r="B367" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C367" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D367" s="9" t="inlineStr">
+        <is>
+          <t>Ferric Oxide Red</t>
+        </is>
+      </c>
+      <c r="E367" s="5" t="n"/>
+      <c r="F367" s="5" t="n"/>
+      <c r="G367" s="5" t="n"/>
+      <c r="H367" s="5" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="9" t="inlineStr">
+        <is>
+          <t>Resmetirom</t>
+        </is>
+      </c>
+      <c r="B368" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C368" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D368" s="9" t="inlineStr">
+        <is>
+          <t>Resmetirom</t>
+        </is>
+      </c>
+      <c r="E368" s="5" t="n"/>
+      <c r="F368" s="5" t="n"/>
+      <c r="G368" s="5" t="n"/>
+      <c r="H368" s="5" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="9" t="inlineStr">
+        <is>
+          <t>Rosuvastatin Calcium</t>
+        </is>
+      </c>
+      <c r="B369" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C369" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D369" s="9" t="inlineStr">
+        <is>
+          <t>Rosuvastatin Calcium</t>
+        </is>
+      </c>
+      <c r="E369" s="5" t="n"/>
+      <c r="F369" s="5" t="n"/>
+      <c r="G369" s="5" t="n"/>
+      <c r="H369" s="5" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="9" t="inlineStr">
+        <is>
+          <t>Sacubitril Valsartan Sodium</t>
+        </is>
+      </c>
+      <c r="B370" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C370" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D370" s="9" t="inlineStr">
+        <is>
+          <t>Sacubitril/Valsartan 3Sodium 2.5H2O Co-crystal</t>
+        </is>
+      </c>
+      <c r="E370" s="5" t="n"/>
+      <c r="F370" s="5" t="n"/>
+      <c r="G370" s="5" t="n"/>
+      <c r="H370" s="5" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="9" t="inlineStr">
+        <is>
+          <t>Sodium benzoate</t>
+        </is>
+      </c>
+      <c r="B371" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C371" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D371" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Benzoate</t>
+        </is>
+      </c>
+      <c r="E371" s="5" t="n"/>
+      <c r="F371" s="5" t="n"/>
+      <c r="G371" s="5" t="n"/>
+      <c r="H371" s="5" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Bicarbonate</t>
+        </is>
+      </c>
+      <c r="B372" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C372" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D372" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Bicarbonate</t>
+        </is>
+      </c>
+      <c r="E372" s="5" t="n"/>
+      <c r="F372" s="5" t="n"/>
+      <c r="G372" s="5" t="n"/>
+      <c r="H372" s="5" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Carboxymethyl Cellulose (CMC)</t>
+        </is>
+      </c>
+      <c r="B373" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C373" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D373" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Carboxymethyl Cellulose (Medium Viscosity)</t>
+        </is>
+      </c>
+      <c r="E373" s="5" t="n"/>
+      <c r="F373" s="5" t="n"/>
+      <c r="G373" s="5" t="n"/>
+      <c r="H373" s="5" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Chloride</t>
+        </is>
+      </c>
+      <c r="B374" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C374" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D374" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Chloride</t>
+        </is>
+      </c>
+      <c r="E374" s="5" t="n"/>
+      <c r="F374" s="5" t="n"/>
+      <c r="G374" s="5" t="n"/>
+      <c r="H374" s="5" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Lauryl Sulfate</t>
+        </is>
+      </c>
+      <c r="B375" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C375" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D375" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Lauryl Sulfate</t>
+        </is>
+      </c>
+      <c r="E375" s="5" t="n"/>
+      <c r="F375" s="5" t="n"/>
+      <c r="G375" s="5" t="n"/>
+      <c r="H375" s="5" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Selenite</t>
+        </is>
+      </c>
+      <c r="B376" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C376" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D376" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Selenite</t>
+        </is>
+      </c>
+      <c r="E376" s="5" t="n"/>
+      <c r="F376" s="5" t="n"/>
+      <c r="G376" s="5" t="n"/>
+      <c r="H376" s="5" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Starch Glycolate</t>
+        </is>
+      </c>
+      <c r="B377" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C377" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D377" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Starch Glycolate</t>
+        </is>
+      </c>
+      <c r="E377" s="5" t="n"/>
+      <c r="F377" s="5" t="n"/>
+      <c r="G377" s="5" t="n"/>
+      <c r="H377" s="5" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Stearyl Fumarate</t>
+        </is>
+      </c>
+      <c r="B378" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C378" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D378" s="9" t="inlineStr">
+        <is>
+          <t>Sodium Stearyl Fumarate</t>
+        </is>
+      </c>
+      <c r="E378" s="5" t="n"/>
+      <c r="F378" s="5" t="n"/>
+      <c r="G378" s="5" t="n"/>
+      <c r="H378" s="5" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="9" t="inlineStr">
+        <is>
+          <t>Sorbitol</t>
+        </is>
+      </c>
+      <c r="B379" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C379" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D379" s="9" t="inlineStr">
+        <is>
+          <t>Sorbitol</t>
+        </is>
+      </c>
+      <c r="E379" s="5" t="n"/>
+      <c r="F379" s="5" t="n"/>
+      <c r="G379" s="5" t="n"/>
+      <c r="H379" s="5" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="9" t="inlineStr">
+        <is>
+          <t>Sorbitol Powder</t>
+        </is>
+      </c>
+      <c r="B380" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C380" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D380" s="9" t="inlineStr">
+        <is>
+          <t>Sorbitol</t>
+        </is>
+      </c>
+      <c r="E380" s="5" t="n"/>
+      <c r="F380" s="5" t="n"/>
+      <c r="G380" s="5" t="n"/>
+      <c r="H380" s="5" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="9" t="inlineStr">
+        <is>
+          <t>Sour cherry Flavour</t>
+        </is>
+      </c>
+      <c r="B381" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C381" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D381" s="9" t="inlineStr">
+        <is>
+          <t>Sour Cherry Flavour</t>
+        </is>
+      </c>
+      <c r="E381" s="5" t="n"/>
+      <c r="F381" s="5" t="n"/>
+      <c r="G381" s="5" t="n"/>
+      <c r="H381" s="5" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="9" t="inlineStr">
+        <is>
+          <t>Strawberry Flavour</t>
+        </is>
+      </c>
+      <c r="B382" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C382" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D382" s="9" t="inlineStr">
+        <is>
+          <t>Strawberry Flavour</t>
+        </is>
+      </c>
+      <c r="E382" s="5" t="n"/>
+      <c r="F382" s="5" t="n"/>
+      <c r="G382" s="5" t="n"/>
+      <c r="H382" s="5" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="9" t="inlineStr">
+        <is>
+          <t>Sucralose</t>
+        </is>
+      </c>
+      <c r="B383" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C383" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D383" s="9" t="inlineStr">
+        <is>
+          <t>Sucralose</t>
+        </is>
+      </c>
+      <c r="E383" s="5" t="n"/>
+      <c r="F383" s="5" t="n"/>
+      <c r="G383" s="5" t="n"/>
+      <c r="H383" s="5" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="9" t="inlineStr">
+        <is>
+          <t>Sunset Yellow</t>
+        </is>
+      </c>
+      <c r="B384" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C384" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D384" s="9" t="inlineStr">
+        <is>
+          <t>Sunset Yellow</t>
+        </is>
+      </c>
+      <c r="E384" s="5" t="n"/>
+      <c r="F384" s="5" t="n"/>
+      <c r="G384" s="5" t="n"/>
+      <c r="H384" s="5" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="9" t="inlineStr">
+        <is>
+          <t>Talc</t>
+        </is>
+      </c>
+      <c r="B385" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C385" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D385" s="9" t="inlineStr">
+        <is>
+          <t>Talc</t>
+        </is>
+      </c>
+      <c r="E385" s="5" t="n"/>
+      <c r="F385" s="5" t="n"/>
+      <c r="G385" s="5" t="n"/>
+      <c r="H385" s="5" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="9" t="inlineStr">
+        <is>
+          <t>Taurine</t>
+        </is>
+      </c>
+      <c r="B386" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C386" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D386" s="9" t="inlineStr">
+        <is>
+          <t>Taurine</t>
+        </is>
+      </c>
+      <c r="E386" s="5" t="n"/>
+      <c r="F386" s="5" t="n"/>
+      <c r="G386" s="5" t="n"/>
+      <c r="H386" s="5" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="9" t="inlineStr">
+        <is>
+          <t>Telmisartan</t>
+        </is>
+      </c>
+      <c r="B387" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C387" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D387" s="9" t="inlineStr">
+        <is>
+          <t>Telmisartan</t>
+        </is>
+      </c>
+      <c r="E387" s="5" t="n"/>
+      <c r="F387" s="5" t="n"/>
+      <c r="G387" s="5" t="n"/>
+      <c r="H387" s="5" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="9" t="inlineStr">
+        <is>
+          <t>Thiamine Hydrochloride (Vit B1)</t>
+        </is>
+      </c>
+      <c r="B388" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C388" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D388" s="9" t="inlineStr">
+        <is>
+          <t>Thiamine Hydrochloride (Vitamin B1)</t>
+        </is>
+      </c>
+      <c r="E388" s="5" t="n"/>
+      <c r="F388" s="5" t="n"/>
+      <c r="G388" s="5" t="n"/>
+      <c r="H388" s="5" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="9" t="inlineStr">
+        <is>
+          <t>Titanium Dioxide</t>
+        </is>
+      </c>
+      <c r="B389" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C389" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D389" s="9" t="inlineStr">
+        <is>
+          <t>Titanium Dioxide</t>
+        </is>
+      </c>
+      <c r="E389" s="5" t="n"/>
+      <c r="F389" s="5" t="n"/>
+      <c r="G389" s="5" t="n"/>
+      <c r="H389" s="5" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="9" t="inlineStr">
+        <is>
+          <t>Triacetin</t>
+        </is>
+      </c>
+      <c r="B390" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C390" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D390" s="9" t="inlineStr">
+        <is>
+          <t>Triacetin</t>
+        </is>
+      </c>
+      <c r="E390" s="5" t="n"/>
+      <c r="F390" s="5" t="n"/>
+      <c r="G390" s="5" t="n"/>
+      <c r="H390" s="5" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin B1(Thiamin Hydrochloride)</t>
+        </is>
+      </c>
+      <c r="B391" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C391" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D391" s="9" t="inlineStr">
+        <is>
+          <t>Thiamine Hydrochloride (Vitamin B1)</t>
+        </is>
+      </c>
+      <c r="E391" s="5" t="n"/>
+      <c r="F391" s="5" t="n"/>
+      <c r="G391" s="5" t="n"/>
+      <c r="H391" s="5" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin B12</t>
+        </is>
+      </c>
+      <c r="B392" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C392" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D392" s="9" t="inlineStr">
+        <is>
+          <t>Cyanocobalamin (Vitamin B12)</t>
+        </is>
+      </c>
+      <c r="E392" s="5" t="n"/>
+      <c r="F392" s="5" t="n"/>
+      <c r="G392" s="5" t="n"/>
+      <c r="H392" s="5" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin B2</t>
+        </is>
+      </c>
+      <c r="B393" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C393" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D393" s="9" t="inlineStr">
+        <is>
+          <t>Riboflavin (Vitamin B2)</t>
+        </is>
+      </c>
+      <c r="E393" s="5" t="n"/>
+      <c r="F393" s="5" t="n"/>
+      <c r="G393" s="5" t="n"/>
+      <c r="H393" s="5" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin B3 (Nicotinamide)</t>
+        </is>
+      </c>
+      <c r="B394" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C394" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D394" s="9" t="inlineStr">
+        <is>
+          <t>Nicotinamide (Vitamin B3)</t>
+        </is>
+      </c>
+      <c r="E394" s="5" t="n"/>
+      <c r="F394" s="5" t="n"/>
+      <c r="G394" s="5" t="n"/>
+      <c r="H394" s="5" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin B5 (D-Calcium- Pantotenate)</t>
+        </is>
+      </c>
+      <c r="B395" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C395" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D395" s="9" t="inlineStr">
+        <is>
+          <t>Calcium Pantothenate (Vitamin B5)</t>
+        </is>
+      </c>
+      <c r="E395" s="5" t="n"/>
+      <c r="F395" s="5" t="n"/>
+      <c r="G395" s="5" t="n"/>
+      <c r="H395" s="5" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin B6 ( Pyridoxine Hydrochloride)</t>
+        </is>
+      </c>
+      <c r="B396" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C396" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D396" s="9" t="inlineStr">
+        <is>
+          <t>Pyridoxine Hydrochloride (Vitamin B6)</t>
+        </is>
+      </c>
+      <c r="E396" s="5" t="n"/>
+      <c r="F396" s="5" t="n"/>
+      <c r="G396" s="5" t="n"/>
+      <c r="H396" s="5" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin B9(Folic Acid)</t>
+        </is>
+      </c>
+      <c r="B397" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C397" s="9" t="inlineStr">
+        <is>
+          <t>In study (DB name mapping)</t>
+        </is>
+      </c>
+      <c r="D397" s="9" t="inlineStr">
+        <is>
+          <t>Folic Acid (Vitamin B9)</t>
+        </is>
+      </c>
+      <c r="E397" s="5" t="n"/>
+      <c r="F397" s="5" t="n"/>
+      <c r="G397" s="5" t="n"/>
+      <c r="H397" s="5" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin D3</t>
+        </is>
+      </c>
+      <c r="B398" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C398" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D398" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin D3</t>
+        </is>
+      </c>
+      <c r="E398" s="5" t="n"/>
+      <c r="F398" s="5" t="n"/>
+      <c r="G398" s="5" t="n"/>
+      <c r="H398" s="5" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="9" t="inlineStr">
+        <is>
+          <t>VITAMIN E</t>
+        </is>
+      </c>
+      <c r="B399" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C399" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D399" s="9" t="inlineStr">
+        <is>
+          <t>D-Alpha Tocopheryl Acetate 50% (Vitamin E)</t>
+        </is>
+      </c>
+      <c r="E399" s="5" t="n"/>
+      <c r="F399" s="5" t="n"/>
+      <c r="G399" s="5" t="n"/>
+      <c r="H399" s="5" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin K1</t>
+        </is>
+      </c>
+      <c r="B400" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C400" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D400" s="9" t="inlineStr">
+        <is>
+          <t>Vitamin K1</t>
+        </is>
+      </c>
+      <c r="E400" s="5" t="n"/>
+      <c r="F400" s="5" t="n"/>
+      <c r="G400" s="5" t="n"/>
+      <c r="H400" s="5" t="n"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="9" t="inlineStr">
+        <is>
+          <t>VITAMINB8(INOSITOL)</t>
+        </is>
+      </c>
+      <c r="B401" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C401" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D401" s="9" t="inlineStr">
+        <is>
+          <t>Inositol (Vitamin B8)</t>
+        </is>
+      </c>
+      <c r="E401" s="5" t="n"/>
+      <c r="F401" s="5" t="n"/>
+      <c r="G401" s="5" t="n"/>
+      <c r="H401" s="5" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="9" t="inlineStr">
+        <is>
+          <t>Yellow Iron Oxide</t>
+        </is>
+      </c>
+      <c r="B402" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C402" s="9" t="inlineStr">
+        <is>
+          <t>In study (Leadtime alias)</t>
+        </is>
+      </c>
+      <c r="D402" s="9" t="inlineStr">
+        <is>
+          <t>Ferric Oxide Yellow</t>
+        </is>
+      </c>
+      <c r="E402" s="5" t="n"/>
+      <c r="F402" s="5" t="n"/>
+      <c r="G402" s="5" t="n"/>
+      <c r="H402" s="5" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="9" t="inlineStr">
+        <is>
+          <t>Zinc Gluconate</t>
+        </is>
+      </c>
+      <c r="B403" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C403" s="9" t="inlineStr">
+        <is>
+          <t>In study</t>
+        </is>
+      </c>
+      <c r="D403" s="9" t="inlineStr">
+        <is>
+          <t>Zinc Gluconate</t>
+        </is>
+      </c>
+      <c r="E403" s="5" t="n"/>
+      <c r="F403" s="5" t="n"/>
+      <c r="G403" s="5" t="n"/>
+      <c r="H403" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H403"/>
+  <dataValidations count="1">
+    <dataValidation sqref="F5:F403" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/questionnaires/RM_Analyst_Questionnaire.xlsx
+++ b/questionnaires/RM_Analyst_Questionnaire.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Materials in Leadtime.xlsx that are not in the study list - still tested?</t>
+          <t>Materials with recorded lab times that are not on the master list - still tested?</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Names from the purchasing list (rawmaterials.md) - confirm the study name, or say if still tested.</t>
+          <t>Names from the purchasing list - confirm the master-list name, or say if still tested.</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>180 materials and 274 material x test rows from QC_Capacity_Study.xlsx (RM_Lots, Test_Times).</t>
+          <t>180 materials on the master list and 274 material x test rows.</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Leadtime.xlsx: 69 exact + 84 alias name matches; 122 materials have a recorded time to confirm.</t>
+          <t>Lab time records: 69 exact + 84 alias name matches; 122 materials have a recorded time to confirm.</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>380 materials appear in Leadtime.xlsx but not in the study list - see 'Other materials'.</t>
+          <t>380 materials have recorded times but are not on the master list - see 'Other materials'.</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>rawmaterials.md: 399 distinct names; 208 Not in study, 87 In study, 59 Suggested - confirm, 19 In study (Leadtime alias), 18 In study (DB name mapping), 8 In Leadtime.xlsx only - see 'Purchase list'.</t>
+          <t>Purchasing list: 399 distinct names; 208 not on master list, 87 on master list, 59 suggested - confirm, 19 on master list (alias), 18 on master list (name mapping), 8 in time records only - see 'Purchase list'.</t>
         </is>
       </c>
     </row>
@@ -729,13 +729,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -768,11 +767,6 @@
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Feeds study sheet / column</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -782,7 +776,6 @@
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -796,11 +789,6 @@
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Personnel A, B, D</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -814,11 +802,6 @@
         </is>
       </c>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Personnel C; Test_Times X</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -832,11 +815,6 @@
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Personnel E, F</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -850,11 +828,6 @@
         </is>
       </c>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Personnel G, H</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
@@ -868,11 +841,6 @@
         </is>
       </c>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Personnel J; Evidence H</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
@@ -886,11 +854,6 @@
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Report: key-person risk</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -900,7 +863,6 @@
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
@@ -914,11 +876,6 @@
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Capacity C (non-routine)</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
@@ -932,11 +889,6 @@
         </is>
       </c>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>RM_Lots D; Evidence B</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
@@ -950,11 +902,6 @@
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Test_Times F (Applicable)</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
@@ -968,11 +915,6 @@
         </is>
       </c>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Capacity C</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -986,11 +928,6 @@
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>RM_Lots H; Capacity C</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1000,7 +937,6 @@
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
@@ -1014,11 +950,6 @@
         </is>
       </c>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Extra tests; Instruments</t>
-        </is>
-      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
@@ -1032,11 +963,6 @@
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Test_Times K-T</t>
-        </is>
-      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
@@ -1050,11 +976,6 @@
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Test_Times I, J</t>
-        </is>
-      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -1068,11 +989,6 @@
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Capacity C</t>
-        </is>
-      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
@@ -1086,11 +1002,6 @@
         </is>
       </c>
       <c r="C23" s="5" t="n"/>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Settings downtime</t>
-        </is>
-      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
@@ -1104,11 +1015,6 @@
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Evidence; Notes</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1118,7 +1024,6 @@
       </c>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
@@ -1132,11 +1037,6 @@
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Evidence E, F, G</t>
-        </is>
-      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
@@ -1150,11 +1050,6 @@
         </is>
       </c>
       <c r="C27" s="5" t="n"/>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>Evidence D</t>
-        </is>
-      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
@@ -1168,11 +1063,6 @@
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>RM_Lots E; Settings growth</t>
-        </is>
-      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
@@ -1186,11 +1076,6 @@
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Capacity C</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -1200,7 +1085,6 @@
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
@@ -1214,11 +1098,6 @@
         </is>
       </c>
       <c r="C31" s="5" t="n"/>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Report_Outline</t>
-        </is>
-      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
@@ -1232,11 +1111,6 @@
         </is>
       </c>
       <c r="C32" s="5" t="n"/>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Report_Outline</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1277,7 +1151,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Columns A-H = RM_Lots sheet of the study. Sorted as in the study; use the filter.</t>
+          <t>One row per material on the master list; use the filter.</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1168,7 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t># products using (from database)</t>
+          <t># products using (from product formulas)</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -1334,17 +1208,17 @@
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>Match to Leadtime.xlsx</t>
+          <t>Match to lab time records</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>Leadtime.xlsx name(s)</t>
+          <t>Name(s) in lab time records</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>Recorded total h/lot (Leadtime, worst variant)</t>
+          <t>Recorded total h/lot (worst supplier variant)</t>
         </is>
       </c>
     </row>
@@ -2063,7 +1937,7 @@
       <c r="J25" s="5" t="n"/>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr"/>
@@ -2127,7 +2001,7 @@
       <c r="J27" s="5" t="n"/>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr"/>
@@ -2296,7 +2170,7 @@
       <c r="J32" s="5" t="n"/>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr"/>
@@ -2395,7 +2269,7 @@
       <c r="J35" s="5" t="n"/>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr"/>
@@ -2667,7 +2541,7 @@
       <c r="J43" s="5" t="n"/>
       <c r="K43" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L43" s="9" t="inlineStr"/>
@@ -2834,7 +2708,7 @@
       <c r="J48" s="5" t="n"/>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr"/>
@@ -2933,7 +2807,7 @@
       <c r="J51" s="5" t="n"/>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr"/>
@@ -3137,7 +3011,7 @@
       <c r="J57" s="5" t="n"/>
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L57" s="9" t="inlineStr"/>
@@ -3409,7 +3283,7 @@
       <c r="J65" s="5" t="n"/>
       <c r="K65" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L65" s="9" t="inlineStr"/>
@@ -3782,7 +3656,7 @@
       <c r="J76" s="5" t="n"/>
       <c r="K76" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L76" s="9" t="inlineStr"/>
@@ -3811,7 +3685,7 @@
       <c r="J77" s="5" t="n"/>
       <c r="K77" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L77" s="9" t="inlineStr"/>
@@ -3910,7 +3784,7 @@
       <c r="J80" s="5" t="n"/>
       <c r="K80" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L80" s="9" t="inlineStr"/>
@@ -4007,7 +3881,7 @@
       <c r="J83" s="5" t="n"/>
       <c r="K83" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L83" s="9" t="inlineStr"/>
@@ -4209,7 +4083,7 @@
       <c r="J89" s="5" t="n"/>
       <c r="K89" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L89" s="9" t="inlineStr"/>
@@ -4761,7 +4635,7 @@
       <c r="J105" s="5" t="n"/>
       <c r="K105" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L105" s="9" t="inlineStr"/>
@@ -4895,7 +4769,7 @@
       <c r="J109" s="5" t="n"/>
       <c r="K109" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L109" s="9" t="inlineStr"/>
@@ -4924,7 +4798,7 @@
       <c r="J110" s="5" t="n"/>
       <c r="K110" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L110" s="9" t="inlineStr"/>
@@ -5021,7 +4895,7 @@
       <c r="J113" s="5" t="n"/>
       <c r="K113" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L113" s="9" t="inlineStr"/>
@@ -5431,7 +5305,7 @@
       <c r="J125" s="5" t="n"/>
       <c r="K125" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L125" s="9" t="inlineStr"/>
@@ -5773,7 +5647,7 @@
       <c r="J135" s="5" t="n"/>
       <c r="K135" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L135" s="9" t="inlineStr"/>
@@ -6251,7 +6125,7 @@
       <c r="J149" s="5" t="n"/>
       <c r="K149" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L149" s="9" t="inlineStr"/>
@@ -6591,7 +6465,7 @@
       <c r="J159" s="5" t="n"/>
       <c r="K159" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L159" s="9" t="inlineStr"/>
@@ -6620,7 +6494,7 @@
       <c r="J160" s="5" t="n"/>
       <c r="K160" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L160" s="9" t="inlineStr"/>
@@ -6715,7 +6589,7 @@
       <c r="J163" s="5" t="n"/>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L163" s="9" t="inlineStr"/>
@@ -6913,7 +6787,7 @@
       <c r="J169" s="5" t="n"/>
       <c r="K169" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L169" s="9" t="inlineStr"/>
@@ -7115,7 +6989,7 @@
       <c r="J175" s="5" t="n"/>
       <c r="K175" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L175" s="9" t="inlineStr"/>
@@ -7313,7 +7187,7 @@
       <c r="J181" s="5" t="n"/>
       <c r="K181" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
       <c r="L181" s="9" t="inlineStr"/>
@@ -7507,14 +7381,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>• Grey columns are pre-filled. Columns AA onward are reference only (e.g. times recorded in Leadtime.xlsx) - confirm or correct them in the yellow columns.</t>
+          <t>• Grey columns are pre-filled. Columns AA onward are reference only (times recorded by the lab in the past) - confirm or correct them in the yellow columns.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>• Columns A-Z are in the same order as the Test_Times sheet of QC_Capacity_Study.xlsx: answers are pasted back 1:1.</t>
+          <t>• Do not insert, delete or reorder columns - the answers are collected by column position.</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7525,7 @@
       </c>
       <c r="AA8" s="10" t="inlineStr">
         <is>
-          <t>Recorded h/sample (Leadtime)</t>
+          <t>Recorded h/sample</t>
         </is>
       </c>
       <c r="AB8" s="10" t="inlineStr">
@@ -10846,7 +10720,7 @@
       <c r="AC49" s="9" t="n"/>
       <c r="AD49" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -10916,7 +10790,7 @@
       <c r="AC50" s="9" t="n"/>
       <c r="AD50" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11020,7 @@
       <c r="AC53" s="9" t="n"/>
       <c r="AD53" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11090,7 @@
       <c r="AC54" s="9" t="n"/>
       <c r="AD54" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11800,7 @@
       <c r="AC63" s="9" t="n"/>
       <c r="AD63" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -11996,7 +11870,7 @@
       <c r="AC64" s="9" t="n"/>
       <c r="AD64" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12260,7 @@
       <c r="AC69" s="9" t="n"/>
       <c r="AD69" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12330,7 @@
       <c r="AC70" s="9" t="n"/>
       <c r="AD70" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13490,7 @@
       <c r="AC85" s="9" t="n"/>
       <c r="AD85" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13560,7 @@
       <c r="AC86" s="9" t="n"/>
       <c r="AD86" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -14376,7 +14250,7 @@
       <c r="AC95" s="9" t="n"/>
       <c r="AD95" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14320,7 @@
       <c r="AC96" s="9" t="n"/>
       <c r="AD96" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -14836,7 +14710,7 @@
       <c r="AC101" s="9" t="n"/>
       <c r="AD101" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -14906,7 +14780,7 @@
       <c r="AC102" s="9" t="n"/>
       <c r="AD102" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -15776,7 +15650,7 @@
       <c r="AC113" s="9" t="n"/>
       <c r="AD113" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15720,7 @@
       <c r="AC114" s="9" t="n"/>
       <c r="AD114" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -17016,7 +16890,7 @@
       <c r="AC129" s="9" t="n"/>
       <c r="AD129" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -17086,7 +16960,7 @@
       <c r="AC130" s="9" t="n"/>
       <c r="AD130" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -18684,7 +18558,7 @@
       <c r="AC151" s="9" t="n"/>
       <c r="AD151" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -18754,7 +18628,7 @@
       <c r="AC152" s="9" t="n"/>
       <c r="AD152" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -18824,7 +18698,7 @@
       <c r="AC153" s="9" t="n"/>
       <c r="AD153" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -18894,7 +18768,7 @@
       <c r="AC154" s="9" t="n"/>
       <c r="AD154" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -19284,7 +19158,7 @@
       <c r="AC159" s="9" t="n"/>
       <c r="AD159" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19228,7 @@
       <c r="AC160" s="9" t="n"/>
       <c r="AD160" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -19724,7 +19598,7 @@
       <c r="AC165" s="9" t="n"/>
       <c r="AD165" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -19794,7 +19668,7 @@
       <c r="AC166" s="9" t="n"/>
       <c r="AD166" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -20644,7 +20518,7 @@
       <c r="AC177" s="9" t="n"/>
       <c r="AD177" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -20714,7 +20588,7 @@
       <c r="AC178" s="9" t="n"/>
       <c r="AD178" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -22722,7 +22596,7 @@
       <c r="AC203" s="9" t="n"/>
       <c r="AD203" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -23048,7 +22922,7 @@
       <c r="AC207" s="9" t="n"/>
       <c r="AD207" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -23122,7 +22996,7 @@
       <c r="AC208" s="9" t="n"/>
       <c r="AD208" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -23358,7 +23232,7 @@
       <c r="AC211" s="9" t="n"/>
       <c r="AD211" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -24344,7 +24218,7 @@
       <c r="AC223" s="9" t="n"/>
       <c r="AD223" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -25168,7 +25042,7 @@
       <c r="AC233" s="9" t="n"/>
       <c r="AD233" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -26316,7 +26190,7 @@
       <c r="AC247" s="9" t="n"/>
       <c r="AD247" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -27134,7 +27008,7 @@
       <c r="AC257" s="9" t="n"/>
       <c r="AD257" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -27208,7 +27082,7 @@
       <c r="AC258" s="9" t="n"/>
       <c r="AD258" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -27438,7 +27312,7 @@
       <c r="AC261" s="9" t="n"/>
       <c r="AD261" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -27914,7 +27788,7 @@
       <c r="AC267" s="9" t="n"/>
       <c r="AD267" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -28402,7 +28276,7 @@
       <c r="AC273" s="9" t="n"/>
       <c r="AD273" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -28878,7 +28752,7 @@
       <c r="AC279" s="9" t="n"/>
       <c r="AD279" s="9" t="inlineStr">
         <is>
-          <t>Not in Leadtime.xlsx</t>
+          <t>No recorded time</t>
         </is>
       </c>
     </row>
@@ -30664,26 +30538,26 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Materials in Leadtime.xlsx that are not in the study list</t>
+          <t>Materials with recorded lab times that are not on the master list</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Is it still purchased and tested? If Y, give lots/yr - it will be added to the study.</t>
+          <t>Is it still purchased and tested? If Y, give lots/yr - it will be added to the master list.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Material (as in Leadtime.xlsx)</t>
+          <t>Material (as in lab time records)</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Leadtime sheet</t>
+          <t>Record group</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -30703,7 +30577,7 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Same material as (study name, if a duplicate)</t>
+          <t>Same material as (master-list name, if a duplicate)</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
@@ -37301,21 +37175,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Raw-material names from the purchasing list (rawmaterials.md)</t>
+          <t>Raw-material names from the purchasing list</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grey = matched automatically. Confirm 'Suggested' rows; for 'Not in study' rows say if QC still tests it and give lots/yr.</t>
+          <t>Grey = matched automatically. Confirm 'Suggested' rows; for 'Not on master list' rows say if QC still tests it and give lots/yr.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Name (as in rawmaterials.md)</t>
+          <t>Name (as purchased)</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -37325,17 +37199,17 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Match to study</t>
+          <t>Match to master list</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Study material</t>
+          <t>Master-list material</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>Correct study name (if wrong / missing)</t>
+          <t>Correct master-list name (if wrong / missing)</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
@@ -38781,7 +38655,7 @@
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D64" s="9" t="n"/>
@@ -38801,7 +38675,7 @@
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D65" s="9" t="n"/>
@@ -38821,7 +38695,7 @@
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D66" s="9" t="n"/>
@@ -38841,7 +38715,7 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D67" s="9" t="n"/>
@@ -38861,7 +38735,7 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D68" s="9" t="n"/>
@@ -38881,7 +38755,7 @@
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D69" s="9" t="n"/>
@@ -38901,7 +38775,7 @@
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D70" s="9" t="n"/>
@@ -38921,7 +38795,7 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D71" s="9" t="n"/>
@@ -38941,7 +38815,7 @@
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D72" s="9" t="n"/>
@@ -38961,7 +38835,7 @@
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D73" s="9" t="n"/>
@@ -38981,7 +38855,7 @@
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D74" s="9" t="n"/>
@@ -39001,7 +38875,7 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D75" s="9" t="n"/>
@@ -39021,7 +38895,7 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D76" s="9" t="n"/>
@@ -39041,7 +38915,7 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D77" s="9" t="n"/>
@@ -39061,7 +38935,7 @@
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D78" s="9" t="n"/>
@@ -39081,7 +38955,7 @@
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D79" s="9" t="n"/>
@@ -39101,7 +38975,7 @@
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D80" s="9" t="n"/>
@@ -39121,7 +38995,7 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D81" s="9" t="n"/>
@@ -39141,7 +39015,7 @@
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D82" s="9" t="n"/>
@@ -39161,7 +39035,7 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D83" s="9" t="n"/>
@@ -39181,7 +39055,7 @@
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D84" s="9" t="n"/>
@@ -39201,7 +39075,7 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D85" s="9" t="n"/>
@@ -39221,7 +39095,7 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D86" s="9" t="n"/>
@@ -39241,7 +39115,7 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D87" s="9" t="n"/>
@@ -39261,7 +39135,7 @@
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D88" s="9" t="n"/>
@@ -39281,7 +39155,7 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D89" s="9" t="n"/>
@@ -39301,7 +39175,7 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D90" s="9" t="n"/>
@@ -39321,7 +39195,7 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D91" s="9" t="n"/>
@@ -39341,7 +39215,7 @@
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D92" s="9" t="n"/>
@@ -39361,7 +39235,7 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D93" s="9" t="n"/>
@@ -39381,7 +39255,7 @@
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D94" s="9" t="n"/>
@@ -39401,7 +39275,7 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D95" s="9" t="n"/>
@@ -39421,7 +39295,7 @@
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D96" s="9" t="n"/>
@@ -39441,7 +39315,7 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D97" s="9" t="n"/>
@@ -39461,7 +39335,7 @@
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D98" s="9" t="n"/>
@@ -39481,7 +39355,7 @@
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D99" s="9" t="n"/>
@@ -39501,7 +39375,7 @@
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D100" s="9" t="n"/>
@@ -39521,7 +39395,7 @@
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D101" s="9" t="n"/>
@@ -39541,7 +39415,7 @@
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D102" s="9" t="n"/>
@@ -39561,7 +39435,7 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D103" s="9" t="n"/>
@@ -39581,7 +39455,7 @@
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D104" s="9" t="n"/>
@@ -39601,7 +39475,7 @@
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D105" s="9" t="n"/>
@@ -39621,7 +39495,7 @@
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D106" s="9" t="n"/>
@@ -39641,7 +39515,7 @@
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D107" s="9" t="n"/>
@@ -39661,7 +39535,7 @@
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D108" s="9" t="n"/>
@@ -39681,7 +39555,7 @@
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D109" s="9" t="n"/>
@@ -39701,7 +39575,7 @@
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D110" s="9" t="n"/>
@@ -39721,7 +39595,7 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D111" s="9" t="n"/>
@@ -39741,7 +39615,7 @@
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D112" s="9" t="n"/>
@@ -39761,7 +39635,7 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D113" s="9" t="n"/>
@@ -39781,7 +39655,7 @@
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D114" s="9" t="n"/>
@@ -39801,7 +39675,7 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D115" s="9" t="n"/>
@@ -39821,7 +39695,7 @@
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D116" s="9" t="n"/>
@@ -39841,7 +39715,7 @@
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D117" s="9" t="n"/>
@@ -39861,7 +39735,7 @@
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D118" s="9" t="n"/>
@@ -39881,7 +39755,7 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D119" s="9" t="n"/>
@@ -39901,7 +39775,7 @@
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D120" s="9" t="n"/>
@@ -39921,7 +39795,7 @@
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D121" s="9" t="n"/>
@@ -39941,7 +39815,7 @@
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D122" s="9" t="n"/>
@@ -39961,7 +39835,7 @@
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D123" s="9" t="n"/>
@@ -39981,7 +39855,7 @@
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D124" s="9" t="n"/>
@@ -40001,7 +39875,7 @@
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D125" s="9" t="n"/>
@@ -40021,7 +39895,7 @@
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D126" s="9" t="n"/>
@@ -40041,7 +39915,7 @@
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D127" s="9" t="n"/>
@@ -40061,7 +39935,7 @@
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D128" s="9" t="n"/>
@@ -40081,7 +39955,7 @@
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D129" s="9" t="n"/>
@@ -40101,7 +39975,7 @@
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D130" s="9" t="n"/>
@@ -40121,7 +39995,7 @@
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D131" s="9" t="n"/>
@@ -40141,7 +40015,7 @@
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D132" s="9" t="n"/>
@@ -40161,7 +40035,7 @@
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D133" s="9" t="n"/>
@@ -40181,7 +40055,7 @@
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D134" s="9" t="n"/>
@@ -40201,7 +40075,7 @@
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D135" s="9" t="n"/>
@@ -40221,7 +40095,7 @@
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D136" s="9" t="n"/>
@@ -40241,7 +40115,7 @@
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D137" s="9" t="n"/>
@@ -40261,7 +40135,7 @@
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D138" s="9" t="n"/>
@@ -40281,7 +40155,7 @@
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D139" s="9" t="n"/>
@@ -40301,7 +40175,7 @@
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D140" s="9" t="n"/>
@@ -40321,7 +40195,7 @@
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D141" s="9" t="n"/>
@@ -40341,7 +40215,7 @@
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D142" s="9" t="n"/>
@@ -40361,7 +40235,7 @@
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D143" s="9" t="n"/>
@@ -40381,7 +40255,7 @@
       </c>
       <c r="C144" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D144" s="9" t="n"/>
@@ -40401,7 +40275,7 @@
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D145" s="9" t="n"/>
@@ -40421,7 +40295,7 @@
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D146" s="9" t="n"/>
@@ -40441,7 +40315,7 @@
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D147" s="9" t="n"/>
@@ -40461,7 +40335,7 @@
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D148" s="9" t="n"/>
@@ -40481,7 +40355,7 @@
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D149" s="9" t="n"/>
@@ -40501,7 +40375,7 @@
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D150" s="9" t="n"/>
@@ -40521,7 +40395,7 @@
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D151" s="9" t="n"/>
@@ -40541,7 +40415,7 @@
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D152" s="9" t="n"/>
@@ -40561,7 +40435,7 @@
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D153" s="9" t="n"/>
@@ -40581,7 +40455,7 @@
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D154" s="9" t="n"/>
@@ -40601,7 +40475,7 @@
       </c>
       <c r="C155" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D155" s="9" t="n"/>
@@ -40621,7 +40495,7 @@
       </c>
       <c r="C156" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D156" s="9" t="n"/>
@@ -40641,7 +40515,7 @@
       </c>
       <c r="C157" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D157" s="9" t="n"/>
@@ -40661,7 +40535,7 @@
       </c>
       <c r="C158" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D158" s="9" t="n"/>
@@ -40681,7 +40555,7 @@
       </c>
       <c r="C159" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D159" s="9" t="n"/>
@@ -40701,7 +40575,7 @@
       </c>
       <c r="C160" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D160" s="9" t="n"/>
@@ -40721,7 +40595,7 @@
       </c>
       <c r="C161" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D161" s="9" t="n"/>
@@ -40741,7 +40615,7 @@
       </c>
       <c r="C162" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D162" s="9" t="n"/>
@@ -40761,7 +40635,7 @@
       </c>
       <c r="C163" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D163" s="9" t="n"/>
@@ -40781,7 +40655,7 @@
       </c>
       <c r="C164" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D164" s="9" t="n"/>
@@ -40801,7 +40675,7 @@
       </c>
       <c r="C165" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D165" s="9" t="n"/>
@@ -40821,7 +40695,7 @@
       </c>
       <c r="C166" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D166" s="9" t="n"/>
@@ -40841,7 +40715,7 @@
       </c>
       <c r="C167" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D167" s="9" t="n"/>
@@ -40861,7 +40735,7 @@
       </c>
       <c r="C168" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D168" s="9" t="n"/>
@@ -40881,7 +40755,7 @@
       </c>
       <c r="C169" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D169" s="9" t="n"/>
@@ -40901,7 +40775,7 @@
       </c>
       <c r="C170" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D170" s="9" t="n"/>
@@ -40921,7 +40795,7 @@
       </c>
       <c r="C171" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D171" s="9" t="n"/>
@@ -40941,7 +40815,7 @@
       </c>
       <c r="C172" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D172" s="9" t="n"/>
@@ -40961,7 +40835,7 @@
       </c>
       <c r="C173" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D173" s="9" t="n"/>
@@ -40981,7 +40855,7 @@
       </c>
       <c r="C174" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D174" s="9" t="n"/>
@@ -41001,7 +40875,7 @@
       </c>
       <c r="C175" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D175" s="9" t="n"/>
@@ -41021,7 +40895,7 @@
       </c>
       <c r="C176" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D176" s="9" t="n"/>
@@ -41041,7 +40915,7 @@
       </c>
       <c r="C177" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D177" s="9" t="n"/>
@@ -41061,7 +40935,7 @@
       </c>
       <c r="C178" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D178" s="9" t="n"/>
@@ -41081,7 +40955,7 @@
       </c>
       <c r="C179" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D179" s="9" t="n"/>
@@ -41101,7 +40975,7 @@
       </c>
       <c r="C180" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D180" s="9" t="n"/>
@@ -41121,7 +40995,7 @@
       </c>
       <c r="C181" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D181" s="9" t="n"/>
@@ -41141,7 +41015,7 @@
       </c>
       <c r="C182" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D182" s="9" t="n"/>
@@ -41161,7 +41035,7 @@
       </c>
       <c r="C183" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D183" s="9" t="n"/>
@@ -41181,7 +41055,7 @@
       </c>
       <c r="C184" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D184" s="9" t="n"/>
@@ -41201,7 +41075,7 @@
       </c>
       <c r="C185" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D185" s="9" t="n"/>
@@ -41221,7 +41095,7 @@
       </c>
       <c r="C186" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D186" s="9" t="n"/>
@@ -41241,7 +41115,7 @@
       </c>
       <c r="C187" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D187" s="9" t="n"/>
@@ -41261,7 +41135,7 @@
       </c>
       <c r="C188" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D188" s="9" t="n"/>
@@ -41281,7 +41155,7 @@
       </c>
       <c r="C189" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D189" s="9" t="n"/>
@@ -41301,7 +41175,7 @@
       </c>
       <c r="C190" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D190" s="9" t="n"/>
@@ -41321,7 +41195,7 @@
       </c>
       <c r="C191" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D191" s="9" t="n"/>
@@ -41341,7 +41215,7 @@
       </c>
       <c r="C192" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D192" s="9" t="n"/>
@@ -41361,7 +41235,7 @@
       </c>
       <c r="C193" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D193" s="9" t="n"/>
@@ -41381,7 +41255,7 @@
       </c>
       <c r="C194" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D194" s="9" t="n"/>
@@ -41401,7 +41275,7 @@
       </c>
       <c r="C195" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D195" s="9" t="n"/>
@@ -41421,7 +41295,7 @@
       </c>
       <c r="C196" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D196" s="9" t="n"/>
@@ -41441,7 +41315,7 @@
       </c>
       <c r="C197" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D197" s="9" t="n"/>
@@ -41461,7 +41335,7 @@
       </c>
       <c r="C198" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D198" s="9" t="n"/>
@@ -41481,7 +41355,7 @@
       </c>
       <c r="C199" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D199" s="9" t="n"/>
@@ -41501,7 +41375,7 @@
       </c>
       <c r="C200" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D200" s="9" t="n"/>
@@ -41521,7 +41395,7 @@
       </c>
       <c r="C201" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D201" s="9" t="n"/>
@@ -41541,7 +41415,7 @@
       </c>
       <c r="C202" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D202" s="9" t="n"/>
@@ -41561,7 +41435,7 @@
       </c>
       <c r="C203" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D203" s="9" t="n"/>
@@ -41581,7 +41455,7 @@
       </c>
       <c r="C204" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D204" s="9" t="n"/>
@@ -41601,7 +41475,7 @@
       </c>
       <c r="C205" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D205" s="9" t="n"/>
@@ -41621,7 +41495,7 @@
       </c>
       <c r="C206" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D206" s="9" t="n"/>
@@ -41641,7 +41515,7 @@
       </c>
       <c r="C207" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D207" s="9" t="n"/>
@@ -41661,7 +41535,7 @@
       </c>
       <c r="C208" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D208" s="9" t="n"/>
@@ -41681,7 +41555,7 @@
       </c>
       <c r="C209" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D209" s="9" t="n"/>
@@ -41701,7 +41575,7 @@
       </c>
       <c r="C210" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D210" s="9" t="n"/>
@@ -41721,7 +41595,7 @@
       </c>
       <c r="C211" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D211" s="9" t="n"/>
@@ -41741,7 +41615,7 @@
       </c>
       <c r="C212" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D212" s="9" t="n"/>
@@ -41761,7 +41635,7 @@
       </c>
       <c r="C213" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D213" s="9" t="n"/>
@@ -41781,7 +41655,7 @@
       </c>
       <c r="C214" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D214" s="9" t="n"/>
@@ -41801,7 +41675,7 @@
       </c>
       <c r="C215" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D215" s="9" t="n"/>
@@ -41821,7 +41695,7 @@
       </c>
       <c r="C216" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D216" s="9" t="n"/>
@@ -41841,7 +41715,7 @@
       </c>
       <c r="C217" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D217" s="9" t="n"/>
@@ -41861,7 +41735,7 @@
       </c>
       <c r="C218" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D218" s="9" t="n"/>
@@ -41881,7 +41755,7 @@
       </c>
       <c r="C219" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D219" s="9" t="n"/>
@@ -41901,7 +41775,7 @@
       </c>
       <c r="C220" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D220" s="9" t="n"/>
@@ -41921,7 +41795,7 @@
       </c>
       <c r="C221" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D221" s="9" t="n"/>
@@ -41941,7 +41815,7 @@
       </c>
       <c r="C222" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D222" s="9" t="n"/>
@@ -41961,7 +41835,7 @@
       </c>
       <c r="C223" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D223" s="9" t="n"/>
@@ -41981,7 +41855,7 @@
       </c>
       <c r="C224" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D224" s="9" t="n"/>
@@ -42001,7 +41875,7 @@
       </c>
       <c r="C225" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D225" s="9" t="n"/>
@@ -42021,7 +41895,7 @@
       </c>
       <c r="C226" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D226" s="9" t="n"/>
@@ -42041,7 +41915,7 @@
       </c>
       <c r="C227" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D227" s="9" t="n"/>
@@ -42061,7 +41935,7 @@
       </c>
       <c r="C228" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D228" s="9" t="n"/>
@@ -42081,7 +41955,7 @@
       </c>
       <c r="C229" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D229" s="9" t="n"/>
@@ -42101,7 +41975,7 @@
       </c>
       <c r="C230" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D230" s="9" t="n"/>
@@ -42121,7 +41995,7 @@
       </c>
       <c r="C231" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D231" s="9" t="n"/>
@@ -42141,7 +42015,7 @@
       </c>
       <c r="C232" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D232" s="9" t="n"/>
@@ -42161,7 +42035,7 @@
       </c>
       <c r="C233" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D233" s="9" t="n"/>
@@ -42181,7 +42055,7 @@
       </c>
       <c r="C234" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D234" s="9" t="n"/>
@@ -42201,7 +42075,7 @@
       </c>
       <c r="C235" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D235" s="9" t="n"/>
@@ -42221,7 +42095,7 @@
       </c>
       <c r="C236" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D236" s="9" t="n"/>
@@ -42241,7 +42115,7 @@
       </c>
       <c r="C237" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D237" s="9" t="n"/>
@@ -42261,7 +42135,7 @@
       </c>
       <c r="C238" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D238" s="9" t="n"/>
@@ -42281,7 +42155,7 @@
       </c>
       <c r="C239" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D239" s="9" t="n"/>
@@ -42301,7 +42175,7 @@
       </c>
       <c r="C240" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D240" s="9" t="n"/>
@@ -42321,7 +42195,7 @@
       </c>
       <c r="C241" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D241" s="9" t="n"/>
@@ -42341,7 +42215,7 @@
       </c>
       <c r="C242" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D242" s="9" t="n"/>
@@ -42361,7 +42235,7 @@
       </c>
       <c r="C243" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D243" s="9" t="n"/>
@@ -42381,7 +42255,7 @@
       </c>
       <c r="C244" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D244" s="9" t="n"/>
@@ -42401,7 +42275,7 @@
       </c>
       <c r="C245" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D245" s="9" t="n"/>
@@ -42421,7 +42295,7 @@
       </c>
       <c r="C246" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D246" s="9" t="n"/>
@@ -42441,7 +42315,7 @@
       </c>
       <c r="C247" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D247" s="9" t="n"/>
@@ -42461,7 +42335,7 @@
       </c>
       <c r="C248" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D248" s="9" t="n"/>
@@ -42481,7 +42355,7 @@
       </c>
       <c r="C249" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D249" s="9" t="n"/>
@@ -42501,7 +42375,7 @@
       </c>
       <c r="C250" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D250" s="9" t="n"/>
@@ -42521,7 +42395,7 @@
       </c>
       <c r="C251" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D251" s="9" t="n"/>
@@ -42541,7 +42415,7 @@
       </c>
       <c r="C252" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D252" s="9" t="n"/>
@@ -42561,7 +42435,7 @@
       </c>
       <c r="C253" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D253" s="9" t="n"/>
@@ -42581,7 +42455,7 @@
       </c>
       <c r="C254" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D254" s="9" t="n"/>
@@ -42601,7 +42475,7 @@
       </c>
       <c r="C255" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D255" s="9" t="n"/>
@@ -42621,7 +42495,7 @@
       </c>
       <c r="C256" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D256" s="9" t="n"/>
@@ -42641,7 +42515,7 @@
       </c>
       <c r="C257" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D257" s="9" t="n"/>
@@ -42661,7 +42535,7 @@
       </c>
       <c r="C258" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D258" s="9" t="n"/>
@@ -42681,7 +42555,7 @@
       </c>
       <c r="C259" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D259" s="9" t="n"/>
@@ -42701,7 +42575,7 @@
       </c>
       <c r="C260" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D260" s="9" t="n"/>
@@ -42721,7 +42595,7 @@
       </c>
       <c r="C261" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D261" s="9" t="n"/>
@@ -42741,7 +42615,7 @@
       </c>
       <c r="C262" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D262" s="9" t="n"/>
@@ -42761,7 +42635,7 @@
       </c>
       <c r="C263" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D263" s="9" t="n"/>
@@ -42781,7 +42655,7 @@
       </c>
       <c r="C264" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D264" s="9" t="n"/>
@@ -42801,7 +42675,7 @@
       </c>
       <c r="C265" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D265" s="9" t="n"/>
@@ -42821,7 +42695,7 @@
       </c>
       <c r="C266" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D266" s="9" t="n"/>
@@ -42841,7 +42715,7 @@
       </c>
       <c r="C267" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D267" s="9" t="n"/>
@@ -42861,7 +42735,7 @@
       </c>
       <c r="C268" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D268" s="9" t="n"/>
@@ -42881,7 +42755,7 @@
       </c>
       <c r="C269" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D269" s="9" t="n"/>
@@ -42901,7 +42775,7 @@
       </c>
       <c r="C270" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D270" s="9" t="n"/>
@@ -42921,7 +42795,7 @@
       </c>
       <c r="C271" s="9" t="inlineStr">
         <is>
-          <t>Not in study</t>
+          <t>Not on master list</t>
         </is>
       </c>
       <c r="D271" s="9" t="n"/>
@@ -42941,7 +42815,7 @@
       </c>
       <c r="C272" s="9" t="inlineStr">
         <is>
-          <t>In Leadtime.xlsx only</t>
+          <t>In time records only</t>
         </is>
       </c>
       <c r="D272" s="9" t="n"/>
@@ -42961,7 +42835,7 @@
       </c>
       <c r="C273" s="9" t="inlineStr">
         <is>
-          <t>In Leadtime.xlsx only</t>
+          <t>In time records only</t>
         </is>
       </c>
       <c r="D273" s="9" t="n"/>
@@ -42981,7 +42855,7 @@
       </c>
       <c r="C274" s="9" t="inlineStr">
         <is>
-          <t>In Leadtime.xlsx only</t>
+          <t>In time records only</t>
         </is>
       </c>
       <c r="D274" s="9" t="n"/>
@@ -43001,7 +42875,7 @@
       </c>
       <c r="C275" s="9" t="inlineStr">
         <is>
-          <t>In Leadtime.xlsx only</t>
+          <t>In time records only</t>
         </is>
       </c>
       <c r="D275" s="9" t="n"/>
@@ -43021,7 +42895,7 @@
       </c>
       <c r="C276" s="9" t="inlineStr">
         <is>
-          <t>In Leadtime.xlsx only</t>
+          <t>In time records only</t>
         </is>
       </c>
       <c r="D276" s="9" t="n"/>
@@ -43041,7 +42915,7 @@
       </c>
       <c r="C277" s="9" t="inlineStr">
         <is>
-          <t>In Leadtime.xlsx only</t>
+          <t>In time records only</t>
         </is>
       </c>
       <c r="D277" s="9" t="n"/>
@@ -43061,7 +42935,7 @@
       </c>
       <c r="C278" s="9" t="inlineStr">
         <is>
-          <t>In Leadtime.xlsx only</t>
+          <t>In time records only</t>
         </is>
       </c>
       <c r="D278" s="9" t="n"/>
@@ -43081,7 +42955,7 @@
       </c>
       <c r="C279" s="9" t="inlineStr">
         <is>
-          <t>In Leadtime.xlsx only</t>
+          <t>In time records only</t>
         </is>
       </c>
       <c r="D279" s="9" t="n"/>
@@ -43101,7 +42975,7 @@
       </c>
       <c r="C280" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
@@ -43125,7 +42999,7 @@
       </c>
       <c r="C281" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
@@ -43149,7 +43023,7 @@
       </c>
       <c r="C282" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
@@ -43173,7 +43047,7 @@
       </c>
       <c r="C283" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
@@ -43197,7 +43071,7 @@
       </c>
       <c r="C284" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D284" s="9" t="inlineStr">
@@ -43221,7 +43095,7 @@
       </c>
       <c r="C285" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
@@ -43245,7 +43119,7 @@
       </c>
       <c r="C286" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
@@ -43269,7 +43143,7 @@
       </c>
       <c r="C287" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D287" s="9" t="inlineStr">
@@ -43293,7 +43167,7 @@
       </c>
       <c r="C288" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D288" s="9" t="inlineStr">
@@ -43317,7 +43191,7 @@
       </c>
       <c r="C289" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
@@ -43341,7 +43215,7 @@
       </c>
       <c r="C290" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
@@ -43365,7 +43239,7 @@
       </c>
       <c r="C291" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
@@ -43389,7 +43263,7 @@
       </c>
       <c r="C292" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
@@ -43413,7 +43287,7 @@
       </c>
       <c r="C293" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
@@ -43437,7 +43311,7 @@
       </c>
       <c r="C294" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
@@ -43461,7 +43335,7 @@
       </c>
       <c r="C295" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D295" s="9" t="inlineStr">
@@ -43485,7 +43359,7 @@
       </c>
       <c r="C296" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D296" s="9" t="inlineStr">
@@ -43509,7 +43383,7 @@
       </c>
       <c r="C297" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
@@ -43533,7 +43407,7 @@
       </c>
       <c r="C298" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
@@ -43557,7 +43431,7 @@
       </c>
       <c r="C299" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
@@ -43581,7 +43455,7 @@
       </c>
       <c r="C300" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D300" s="9" t="inlineStr">
@@ -43605,7 +43479,7 @@
       </c>
       <c r="C301" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
@@ -43629,7 +43503,7 @@
       </c>
       <c r="C302" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
@@ -43653,7 +43527,7 @@
       </c>
       <c r="C303" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
@@ -43677,7 +43551,7 @@
       </c>
       <c r="C304" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
@@ -43701,7 +43575,7 @@
       </c>
       <c r="C305" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
@@ -43725,7 +43599,7 @@
       </c>
       <c r="C306" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D306" s="9" t="inlineStr">
@@ -43749,7 +43623,7 @@
       </c>
       <c r="C307" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
@@ -43773,7 +43647,7 @@
       </c>
       <c r="C308" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
@@ -43797,7 +43671,7 @@
       </c>
       <c r="C309" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
@@ -43821,7 +43695,7 @@
       </c>
       <c r="C310" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D310" s="9" t="inlineStr">
@@ -43845,7 +43719,7 @@
       </c>
       <c r="C311" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D311" s="9" t="inlineStr">
@@ -43869,7 +43743,7 @@
       </c>
       <c r="C312" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D312" s="9" t="inlineStr">
@@ -43893,7 +43767,7 @@
       </c>
       <c r="C313" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
@@ -43917,7 +43791,7 @@
       </c>
       <c r="C314" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
@@ -43941,7 +43815,7 @@
       </c>
       <c r="C315" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
@@ -43965,7 +43839,7 @@
       </c>
       <c r="C316" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
@@ -43989,7 +43863,7 @@
       </c>
       <c r="C317" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D317" s="9" t="inlineStr">
@@ -44013,7 +43887,7 @@
       </c>
       <c r="C318" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
@@ -44037,7 +43911,7 @@
       </c>
       <c r="C319" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
@@ -44061,7 +43935,7 @@
       </c>
       <c r="C320" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
@@ -44085,7 +43959,7 @@
       </c>
       <c r="C321" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
@@ -44109,7 +43983,7 @@
       </c>
       <c r="C322" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D322" s="9" t="inlineStr">
@@ -44133,7 +44007,7 @@
       </c>
       <c r="C323" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D323" s="9" t="inlineStr">
@@ -44157,7 +44031,7 @@
       </c>
       <c r="C324" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D324" s="9" t="inlineStr">
@@ -44181,7 +44055,7 @@
       </c>
       <c r="C325" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D325" s="9" t="inlineStr">
@@ -44205,7 +44079,7 @@
       </c>
       <c r="C326" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D326" s="9" t="inlineStr">
@@ -44229,7 +44103,7 @@
       </c>
       <c r="C327" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D327" s="9" t="inlineStr">
@@ -44253,7 +44127,7 @@
       </c>
       <c r="C328" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D328" s="9" t="inlineStr">
@@ -44277,7 +44151,7 @@
       </c>
       <c r="C329" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D329" s="9" t="inlineStr">
@@ -44301,7 +44175,7 @@
       </c>
       <c r="C330" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D330" s="9" t="inlineStr">
@@ -44325,7 +44199,7 @@
       </c>
       <c r="C331" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D331" s="9" t="inlineStr">
@@ -44349,7 +44223,7 @@
       </c>
       <c r="C332" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D332" s="9" t="inlineStr">
@@ -44373,7 +44247,7 @@
       </c>
       <c r="C333" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D333" s="9" t="inlineStr">
@@ -44397,7 +44271,7 @@
       </c>
       <c r="C334" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D334" s="9" t="inlineStr">
@@ -44421,7 +44295,7 @@
       </c>
       <c r="C335" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D335" s="9" t="inlineStr">
@@ -44445,7 +44319,7 @@
       </c>
       <c r="C336" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D336" s="9" t="inlineStr">
@@ -44469,7 +44343,7 @@
       </c>
       <c r="C337" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D337" s="9" t="inlineStr">
@@ -44493,7 +44367,7 @@
       </c>
       <c r="C338" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D338" s="9" t="inlineStr">
@@ -44517,7 +44391,7 @@
       </c>
       <c r="C339" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D339" s="9" t="inlineStr">
@@ -44541,7 +44415,7 @@
       </c>
       <c r="C340" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D340" s="9" t="inlineStr">
@@ -44565,7 +44439,7 @@
       </c>
       <c r="C341" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D341" s="9" t="inlineStr">
@@ -44589,7 +44463,7 @@
       </c>
       <c r="C342" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D342" s="9" t="inlineStr">
@@ -44613,7 +44487,7 @@
       </c>
       <c r="C343" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D343" s="9" t="inlineStr">
@@ -44637,7 +44511,7 @@
       </c>
       <c r="C344" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D344" s="9" t="inlineStr">
@@ -44661,7 +44535,7 @@
       </c>
       <c r="C345" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D345" s="9" t="inlineStr">
@@ -44685,7 +44559,7 @@
       </c>
       <c r="C346" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D346" s="9" t="inlineStr">
@@ -44709,7 +44583,7 @@
       </c>
       <c r="C347" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D347" s="9" t="inlineStr">
@@ -44733,7 +44607,7 @@
       </c>
       <c r="C348" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D348" s="9" t="inlineStr">
@@ -44757,7 +44631,7 @@
       </c>
       <c r="C349" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D349" s="9" t="inlineStr">
@@ -44781,7 +44655,7 @@
       </c>
       <c r="C350" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D350" s="9" t="inlineStr">
@@ -44805,7 +44679,7 @@
       </c>
       <c r="C351" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D351" s="9" t="inlineStr">
@@ -44829,7 +44703,7 @@
       </c>
       <c r="C352" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D352" s="9" t="inlineStr">
@@ -44853,7 +44727,7 @@
       </c>
       <c r="C353" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D353" s="9" t="inlineStr">
@@ -44877,7 +44751,7 @@
       </c>
       <c r="C354" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D354" s="9" t="inlineStr">
@@ -44901,7 +44775,7 @@
       </c>
       <c r="C355" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D355" s="9" t="inlineStr">
@@ -44925,7 +44799,7 @@
       </c>
       <c r="C356" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D356" s="9" t="inlineStr">
@@ -44949,7 +44823,7 @@
       </c>
       <c r="C357" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D357" s="9" t="inlineStr">
@@ -44973,7 +44847,7 @@
       </c>
       <c r="C358" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D358" s="9" t="inlineStr">
@@ -44997,7 +44871,7 @@
       </c>
       <c r="C359" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D359" s="9" t="inlineStr">
@@ -45021,7 +44895,7 @@
       </c>
       <c r="C360" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D360" s="9" t="inlineStr">
@@ -45045,7 +44919,7 @@
       </c>
       <c r="C361" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D361" s="9" t="inlineStr">
@@ -45069,7 +44943,7 @@
       </c>
       <c r="C362" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D362" s="9" t="inlineStr">
@@ -45093,7 +44967,7 @@
       </c>
       <c r="C363" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D363" s="9" t="inlineStr">
@@ -45117,7 +44991,7 @@
       </c>
       <c r="C364" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D364" s="9" t="inlineStr">
@@ -45141,7 +45015,7 @@
       </c>
       <c r="C365" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D365" s="9" t="inlineStr">
@@ -45165,7 +45039,7 @@
       </c>
       <c r="C366" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D366" s="9" t="inlineStr">
@@ -45189,7 +45063,7 @@
       </c>
       <c r="C367" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D367" s="9" t="inlineStr">
@@ -45213,7 +45087,7 @@
       </c>
       <c r="C368" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D368" s="9" t="inlineStr">
@@ -45237,7 +45111,7 @@
       </c>
       <c r="C369" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D369" s="9" t="inlineStr">
@@ -45261,7 +45135,7 @@
       </c>
       <c r="C370" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D370" s="9" t="inlineStr">
@@ -45285,7 +45159,7 @@
       </c>
       <c r="C371" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D371" s="9" t="inlineStr">
@@ -45309,7 +45183,7 @@
       </c>
       <c r="C372" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D372" s="9" t="inlineStr">
@@ -45333,7 +45207,7 @@
       </c>
       <c r="C373" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D373" s="9" t="inlineStr">
@@ -45357,7 +45231,7 @@
       </c>
       <c r="C374" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D374" s="9" t="inlineStr">
@@ -45381,7 +45255,7 @@
       </c>
       <c r="C375" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D375" s="9" t="inlineStr">
@@ -45405,7 +45279,7 @@
       </c>
       <c r="C376" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D376" s="9" t="inlineStr">
@@ -45429,7 +45303,7 @@
       </c>
       <c r="C377" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D377" s="9" t="inlineStr">
@@ -45453,7 +45327,7 @@
       </c>
       <c r="C378" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D378" s="9" t="inlineStr">
@@ -45477,7 +45351,7 @@
       </c>
       <c r="C379" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D379" s="9" t="inlineStr">
@@ -45501,7 +45375,7 @@
       </c>
       <c r="C380" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D380" s="9" t="inlineStr">
@@ -45525,7 +45399,7 @@
       </c>
       <c r="C381" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D381" s="9" t="inlineStr">
@@ -45549,7 +45423,7 @@
       </c>
       <c r="C382" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D382" s="9" t="inlineStr">
@@ -45573,7 +45447,7 @@
       </c>
       <c r="C383" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D383" s="9" t="inlineStr">
@@ -45597,7 +45471,7 @@
       </c>
       <c r="C384" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D384" s="9" t="inlineStr">
@@ -45621,7 +45495,7 @@
       </c>
       <c r="C385" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D385" s="9" t="inlineStr">
@@ -45645,7 +45519,7 @@
       </c>
       <c r="C386" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D386" s="9" t="inlineStr">
@@ -45669,7 +45543,7 @@
       </c>
       <c r="C387" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D387" s="9" t="inlineStr">
@@ -45693,7 +45567,7 @@
       </c>
       <c r="C388" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D388" s="9" t="inlineStr">
@@ -45717,7 +45591,7 @@
       </c>
       <c r="C389" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D389" s="9" t="inlineStr">
@@ -45741,7 +45615,7 @@
       </c>
       <c r="C390" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D390" s="9" t="inlineStr">
@@ -45765,7 +45639,7 @@
       </c>
       <c r="C391" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D391" s="9" t="inlineStr">
@@ -45789,7 +45663,7 @@
       </c>
       <c r="C392" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D392" s="9" t="inlineStr">
@@ -45813,7 +45687,7 @@
       </c>
       <c r="C393" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D393" s="9" t="inlineStr">
@@ -45837,7 +45711,7 @@
       </c>
       <c r="C394" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D394" s="9" t="inlineStr">
@@ -45861,7 +45735,7 @@
       </c>
       <c r="C395" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D395" s="9" t="inlineStr">
@@ -45885,7 +45759,7 @@
       </c>
       <c r="C396" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D396" s="9" t="inlineStr">
@@ -45909,7 +45783,7 @@
       </c>
       <c r="C397" s="9" t="inlineStr">
         <is>
-          <t>In study (DB name mapping)</t>
+          <t>On master list (name mapping)</t>
         </is>
       </c>
       <c r="D397" s="9" t="inlineStr">
@@ -45933,7 +45807,7 @@
       </c>
       <c r="C398" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D398" s="9" t="inlineStr">
@@ -45957,7 +45831,7 @@
       </c>
       <c r="C399" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D399" s="9" t="inlineStr">
@@ -45981,7 +45855,7 @@
       </c>
       <c r="C400" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D400" s="9" t="inlineStr">
@@ -46005,7 +45879,7 @@
       </c>
       <c r="C401" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D401" s="9" t="inlineStr">
@@ -46029,7 +45903,7 @@
       </c>
       <c r="C402" s="9" t="inlineStr">
         <is>
-          <t>In study (Leadtime alias)</t>
+          <t>On master list (alias)</t>
         </is>
       </c>
       <c r="D402" s="9" t="inlineStr">
@@ -46053,7 +45927,7 @@
       </c>
       <c r="C403" s="9" t="inlineStr">
         <is>
-          <t>In study</t>
+          <t>On master list</t>
         </is>
       </c>
       <c r="D403" s="9" t="inlineStr">
